--- a/data/airports/Export APT 4.xlsx
+++ b/data/airports/Export APT 4.xlsx
@@ -77,16 +77,16 @@
     <t>Country</t>
   </si>
   <si>
-    <t>** MSFS_Addons_Linker ** (5 / 235)</t>
+    <t>** MSFS_Addons_Linker ** (6 / 235)</t>
   </si>
   <si>
     <t>Open</t>
   </si>
   <si>
-    <t>Aeroports (2 / 230)</t>
-  </si>
-  <si>
-    <t>AFRIQUE (1 / 13)</t>
+    <t>Aeroports (3 / 230)</t>
+  </si>
+  <si>
+    <t>AFRIQUE (2 / 13)</t>
   </si>
   <si>
     <t>ALGERIE (0 / 1)</t>
@@ -119,7 +119,7 @@
     <t>No</t>
   </si>
   <si>
-    <t>ARABIE SAOUDITE (0 / 3)</t>
+    <t>ARABIE SAOUDITE (1 / 3)</t>
   </si>
   <si>
     <t>inibuilds-airport-omdu-skydive-dubai</t>
@@ -152,6 +152,9 @@
     <t>azrsim</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>inibuilds-airport-omdb-dubai</t>
   </si>
   <si>
@@ -200,9 +203,6 @@
     <t>Sim Design Group</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>MAROC (0 / 2)</t>
   </si>
   <si>
@@ -941,7 +941,16 @@
     <t>LCLK Larnaca International</t>
   </si>
   <si>
-    <t>CROATIE (0 / 3)</t>
+    <t>CROATIE (0 / 4)</t>
+  </si>
+  <si>
+    <t>davorpuljevic-airport-ldsp-split</t>
+  </si>
+  <si>
+    <t>LDSP</t>
+  </si>
+  <si>
+    <t>Puljevic</t>
   </si>
   <si>
     <t>davorpuljevic-airport-lddu-dubrovnik</t>
@@ -950,9 +959,6 @@
     <t>LDDU</t>
   </si>
   <si>
-    <t>Puljevic</t>
-  </si>
-  <si>
     <t>inibuilds-airport-lddu-dubrovnik</t>
   </si>
   <si>
@@ -992,7 +998,7 @@
     <t>SimNord</t>
   </si>
   <si>
-    <t>ESPAGNE (0 / 10)</t>
+    <t>ESPAGNE (0 / 9)</t>
   </si>
   <si>
     <t>mkstudios-airport-gcfv-fuerteventura</t>
@@ -1091,6 +1097,318 @@
     <t>LEZL Sevilla Airport</t>
   </si>
   <si>
+    <t>ESTONIE (0 / 1)</t>
+  </si>
+  <si>
+    <t>drzewieckidesign-airport-eetn-tallinn</t>
+  </si>
+  <si>
+    <t>EETN</t>
+  </si>
+  <si>
+    <t>EETN Tallinn</t>
+  </si>
+  <si>
+    <t>Drzewiecki Design</t>
+  </si>
+  <si>
+    <t>FINLANDE (0 / 2)</t>
+  </si>
+  <si>
+    <t>mkstudios-airport-efhk-helsinki</t>
+  </si>
+  <si>
+    <t>EFHK</t>
+  </si>
+  <si>
+    <t>EFHK Helsinki Vantaa</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t>mkstudios-airport-efro-rovaniemi</t>
+  </si>
+  <si>
+    <t>EFRO</t>
+  </si>
+  <si>
+    <t>2.0.4</t>
+  </si>
+  <si>
+    <t>EFRO Rovaniemi Airport</t>
+  </si>
+  <si>
+    <t>FRANCE (1 / 27)</t>
+  </si>
+  <si>
+    <t>pilotexperiencesim-airport-lfbd-bordeaux-merignac</t>
+  </si>
+  <si>
+    <t>LFBD</t>
+  </si>
+  <si>
+    <t>2.1.1</t>
+  </si>
+  <si>
+    <t>LFBD Bordeaux-Mérignac Airport</t>
+  </si>
+  <si>
+    <t>Pilot Experience Sim</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>flightbeam-airport-lfbo-toulouse</t>
+  </si>
+  <si>
+    <t>LFBO</t>
+  </si>
+  <si>
+    <t>LFBO Toulouse Blagnac Airport</t>
+  </si>
+  <si>
+    <t>Flightbeam</t>
+  </si>
+  <si>
+    <t>francevfr-airport-lfjl-metz-nancy</t>
+  </si>
+  <si>
+    <t>LFJL</t>
+  </si>
+  <si>
+    <t>LFJL Metz-Nancy Lorraine Airport</t>
+  </si>
+  <si>
+    <t>France VFR</t>
+  </si>
+  <si>
+    <t>francevfr-airport-lfkb-bastia-poretta</t>
+  </si>
+  <si>
+    <t>LFKB</t>
+  </si>
+  <si>
+    <t>LFKB Bastia Poretta Airport</t>
+  </si>
+  <si>
+    <t>francevfr-airport-lfkc-calvi-sainte-catherine</t>
+  </si>
+  <si>
+    <t>LFKC</t>
+  </si>
+  <si>
+    <t>LFKC Calvi Sainte-Catherine</t>
+  </si>
+  <si>
+    <t>fsx3d-airport-lfkc-calvi-sainte-catherine</t>
+  </si>
+  <si>
+    <t>1.6.0</t>
+  </si>
+  <si>
+    <t>LFKC Calvi St. Catherine Airport</t>
+  </si>
+  <si>
+    <t>FSX3D</t>
+  </si>
+  <si>
+    <t>vref-airport-lfkc-calvi-sainte-catherine</t>
+  </si>
+  <si>
+    <t>LFKC Calvi St.Catherine Airport</t>
+  </si>
+  <si>
+    <t>Vref Simulations</t>
+  </si>
+  <si>
+    <t>francevfr-airport-lfkf-figari</t>
+  </si>
+  <si>
+    <t>LFKF</t>
+  </si>
+  <si>
+    <t>LFKF Figari Sud Corse Airport</t>
+  </si>
+  <si>
+    <t>francevfr-airport-lfkj-ajaccio</t>
+  </si>
+  <si>
+    <t>LFKJ</t>
+  </si>
+  <si>
+    <t>LFKJ Ajaccio Napoleon Bonaparte Airport</t>
+  </si>
+  <si>
+    <t>pilotexperiencesim-airport-lfkj-ajaccio</t>
+  </si>
+  <si>
+    <t>LFKJ Ajaccio Airport</t>
+  </si>
+  <si>
+    <t>fsx3d-airport-lfkt-corte</t>
+  </si>
+  <si>
+    <t>LFKT</t>
+  </si>
+  <si>
+    <t>LFKT Corte</t>
+  </si>
+  <si>
+    <t>francevfr-airport-lflb-chambery</t>
+  </si>
+  <si>
+    <t>LFLB</t>
+  </si>
+  <si>
+    <t>LFLB Chambéry Savoie Mont-Blanc Airport</t>
+  </si>
+  <si>
+    <t>mxidesign-airport-lflb-chambery</t>
+  </si>
+  <si>
+    <t>LFLB-Chambery Aix Les Bains</t>
+  </si>
+  <si>
+    <t>flydesign-airport-lfmd-cannes-mandelieu</t>
+  </si>
+  <si>
+    <t>LFMD</t>
+  </si>
+  <si>
+    <t>FlyDesign LFMD Cannes-Mandelieu Airport</t>
+  </si>
+  <si>
+    <t>FlyDesign</t>
+  </si>
+  <si>
+    <t>rdpresets-airport-lfml-marseille</t>
+  </si>
+  <si>
+    <t>LFML</t>
+  </si>
+  <si>
+    <t>LFML Marseille Provence Airport</t>
+  </si>
+  <si>
+    <t>justsim-airport-lfmn-nice-cote-d-azur</t>
+  </si>
+  <si>
+    <t>LFMN</t>
+  </si>
+  <si>
+    <t>2.3.2</t>
+  </si>
+  <si>
+    <t>LFMN Nice Cote d'Azur airport NG series</t>
+  </si>
+  <si>
+    <t>justsim</t>
+  </si>
+  <si>
+    <t>PUR justsim-airport-lfmn-nice</t>
+  </si>
+  <si>
+    <t>pilotexperiencesim-airport-lfmt-montpellier-mediterranee</t>
+  </si>
+  <si>
+    <t>LFMT</t>
+  </si>
+  <si>
+    <t>LFMT Montpellier Airport</t>
+  </si>
+  <si>
+    <t>fsx3d-airport-lfna-gap-tallard</t>
+  </si>
+  <si>
+    <t>LFNA</t>
+  </si>
+  <si>
+    <t>LFNA Gap Tallard</t>
+  </si>
+  <si>
+    <t>fsdreamteam-airport-lfnc-mont-dauphin</t>
+  </si>
+  <si>
+    <t>LFNC</t>
+  </si>
+  <si>
+    <t>LFNC Mont-Dauphin - Saint-Crépin Airport</t>
+  </si>
+  <si>
+    <t>Fsdreamteam</t>
+  </si>
+  <si>
+    <t>fsx3d-airport-lfnc-saint-crepin</t>
+  </si>
+  <si>
+    <t>LFNC Saint-Crepin</t>
+  </si>
+  <si>
+    <t>jetstream-airport-lfpo-paris-orly</t>
+  </si>
+  <si>
+    <t>LFPO</t>
+  </si>
+  <si>
+    <t>Paris Orly LFPO</t>
+  </si>
+  <si>
+    <t>JetStream Designs</t>
+  </si>
+  <si>
+    <t>francevfr-airport-lfrn-rennes</t>
+  </si>
+  <si>
+    <t>LFRN</t>
+  </si>
+  <si>
+    <t>LFRN Rennes Bretagne Airport</t>
+  </si>
+  <si>
+    <t>francevfr-airport-lfrs-nantes</t>
+  </si>
+  <si>
+    <t>LFRS</t>
+  </si>
+  <si>
+    <t>LFRS Nantes</t>
+  </si>
+  <si>
+    <t>francevfr-airport-lfsb-basel</t>
+  </si>
+  <si>
+    <t>LFSB</t>
+  </si>
+  <si>
+    <t>LFSB Basel-Mulhouse-Freiburg EuroAirport</t>
+  </si>
+  <si>
+    <t>francevfr-airport-lfst-strasbourg</t>
+  </si>
+  <si>
+    <t>LFST</t>
+  </si>
+  <si>
+    <t>1.3.3</t>
+  </si>
+  <si>
+    <t>LFST Strasbourg-Entzheim Airport</t>
+  </si>
+  <si>
+    <t>pilotexperiencesim-airport-lftz-st-tropez</t>
+  </si>
+  <si>
+    <t>LFTZ</t>
+  </si>
+  <si>
+    <t>LFTZ Saint Tropez</t>
+  </si>
+  <si>
+    <t>GIBRALTAR (0 / 1)</t>
+  </si>
+  <si>
     <t>rdpresets-airport-lxgb-gibraltar</t>
   </si>
   <si>
@@ -1101,318 +1419,6 @@
   </si>
   <si>
     <t>Gibraltar</t>
-  </si>
-  <si>
-    <t>ESTONIE (0 / 1)</t>
-  </si>
-  <si>
-    <t>drzewieckidesign-airport-eetn-tallinn</t>
-  </si>
-  <si>
-    <t>EETN</t>
-  </si>
-  <si>
-    <t>EETN Tallinn</t>
-  </si>
-  <si>
-    <t>Drzewiecki Design</t>
-  </si>
-  <si>
-    <t>FINLANDE (0 / 2)</t>
-  </si>
-  <si>
-    <t>mkstudios-airport-efhk-helsinki</t>
-  </si>
-  <si>
-    <t>EFHK</t>
-  </si>
-  <si>
-    <t>EFHK Helsinki Vantaa</t>
-  </si>
-  <si>
-    <t>Finland</t>
-  </si>
-  <si>
-    <t>mkstudios-airport-efro-rovaniemi</t>
-  </si>
-  <si>
-    <t>EFRO</t>
-  </si>
-  <si>
-    <t>2.0.4</t>
-  </si>
-  <si>
-    <t>EFRO Rovaniemi Airport</t>
-  </si>
-  <si>
-    <t>FRANCE (1 / 27)</t>
-  </si>
-  <si>
-    <t>pilotexperiencesim-airport-lfbd-bordeaux-merignac</t>
-  </si>
-  <si>
-    <t>LFBD</t>
-  </si>
-  <si>
-    <t>2.1.1</t>
-  </si>
-  <si>
-    <t>LFBD Bordeaux-Mérignac Airport</t>
-  </si>
-  <si>
-    <t>Pilot Experience Sim</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>flightbeam-airport-lfbo-toulouse</t>
-  </si>
-  <si>
-    <t>LFBO</t>
-  </si>
-  <si>
-    <t>LFBO Toulouse Blagnac Airport</t>
-  </si>
-  <si>
-    <t>Flightbeam</t>
-  </si>
-  <si>
-    <t>francevfr-airport-lfjl-metz-nancy</t>
-  </si>
-  <si>
-    <t>LFJL</t>
-  </si>
-  <si>
-    <t>LFJL Metz-Nancy Lorraine Airport</t>
-  </si>
-  <si>
-    <t>France VFR</t>
-  </si>
-  <si>
-    <t>francevfr-airport-lfkb-bastia-poretta</t>
-  </si>
-  <si>
-    <t>LFKB</t>
-  </si>
-  <si>
-    <t>LFKB Bastia Poretta Airport</t>
-  </si>
-  <si>
-    <t>francevfr-airport-lfkc-calvi-sainte-catherine</t>
-  </si>
-  <si>
-    <t>LFKC</t>
-  </si>
-  <si>
-    <t>LFKC Calvi Sainte-Catherine</t>
-  </si>
-  <si>
-    <t>fsx3d-airport-lfkc-calvi-sainte-catherine</t>
-  </si>
-  <si>
-    <t>1.6.0</t>
-  </si>
-  <si>
-    <t>LFKC Calvi St. Catherine Airport</t>
-  </si>
-  <si>
-    <t>FSX3D</t>
-  </si>
-  <si>
-    <t>vref-airport-lfkc-calvi-sainte-catherine</t>
-  </si>
-  <si>
-    <t>LFKC Calvi St.Catherine Airport</t>
-  </si>
-  <si>
-    <t>Vref Simulations</t>
-  </si>
-  <si>
-    <t>francevfr-airport-lfkf-figari</t>
-  </si>
-  <si>
-    <t>LFKF</t>
-  </si>
-  <si>
-    <t>LFKF Figari Sud Corse Airport</t>
-  </si>
-  <si>
-    <t>francevfr-airport-lfkj-ajaccio</t>
-  </si>
-  <si>
-    <t>LFKJ</t>
-  </si>
-  <si>
-    <t>LFKJ Ajaccio Napoleon Bonaparte Airport</t>
-  </si>
-  <si>
-    <t>pilotexperiencesim-airport-lfkj-ajaccio</t>
-  </si>
-  <si>
-    <t>LFKJ Ajaccio Airport</t>
-  </si>
-  <si>
-    <t>fsx3d-airport-lfkt-corte</t>
-  </si>
-  <si>
-    <t>LFKT</t>
-  </si>
-  <si>
-    <t>LFKT Corte</t>
-  </si>
-  <si>
-    <t>francevfr-airport-lflb-chambery</t>
-  </si>
-  <si>
-    <t>LFLB</t>
-  </si>
-  <si>
-    <t>LFLB Chambéry Savoie Mont-Blanc Airport</t>
-  </si>
-  <si>
-    <t>mxidesign-airport-lflb-chambery</t>
-  </si>
-  <si>
-    <t>LFLB-Chambery Aix Les Bains</t>
-  </si>
-  <si>
-    <t>flydesign-airport-lfmd-cannes-mandelieu</t>
-  </si>
-  <si>
-    <t>LFMD</t>
-  </si>
-  <si>
-    <t>FlyDesign LFMD Cannes-Mandelieu Airport</t>
-  </si>
-  <si>
-    <t>FlyDesign</t>
-  </si>
-  <si>
-    <t>rdpresets-airport-lfml-marseille</t>
-  </si>
-  <si>
-    <t>LFML</t>
-  </si>
-  <si>
-    <t>LFML Marseille Provence Airport</t>
-  </si>
-  <si>
-    <t>justsim-airport-lfmn-nice-cote-d-azur</t>
-  </si>
-  <si>
-    <t>LFMN</t>
-  </si>
-  <si>
-    <t>2.3.2</t>
-  </si>
-  <si>
-    <t>LFMN Nice Cote d'Azur airport NG series</t>
-  </si>
-  <si>
-    <t>justsim</t>
-  </si>
-  <si>
-    <t>PUR justsim-airport-lfmn-nice</t>
-  </si>
-  <si>
-    <t>pilotexperiencesim-airport-lfmt-montpellier-mediterranee</t>
-  </si>
-  <si>
-    <t>LFMT</t>
-  </si>
-  <si>
-    <t>LFMT Montpellier Airport</t>
-  </si>
-  <si>
-    <t>fsx3d-airport-lfna-gap-tallard</t>
-  </si>
-  <si>
-    <t>LFNA</t>
-  </si>
-  <si>
-    <t>LFNA Gap Tallard</t>
-  </si>
-  <si>
-    <t>fsdreamteam-airport-lfnc-mont-dauphin</t>
-  </si>
-  <si>
-    <t>LFNC</t>
-  </si>
-  <si>
-    <t>LFNC Mont-Dauphin - Saint-Crépin Airport</t>
-  </si>
-  <si>
-    <t>Fsdreamteam</t>
-  </si>
-  <si>
-    <t>fsx3d-airport-lfnc-saint-crepin</t>
-  </si>
-  <si>
-    <t>LFNC Saint-Crepin</t>
-  </si>
-  <si>
-    <t>jetstream-airport-lfpo-paris-orly</t>
-  </si>
-  <si>
-    <t>LFPO</t>
-  </si>
-  <si>
-    <t>Paris Orly LFPO</t>
-  </si>
-  <si>
-    <t>JetStream Designs</t>
-  </si>
-  <si>
-    <t>francevfr-airport-lfrn-rennes</t>
-  </si>
-  <si>
-    <t>LFRN</t>
-  </si>
-  <si>
-    <t>LFRN Rennes Bretagne Airport</t>
-  </si>
-  <si>
-    <t>francevfr-airport-lfrs-nantes</t>
-  </si>
-  <si>
-    <t>LFRS</t>
-  </si>
-  <si>
-    <t>LFRS Nantes</t>
-  </si>
-  <si>
-    <t>francevfr-airport-lfsb-basel</t>
-  </si>
-  <si>
-    <t>LFSB</t>
-  </si>
-  <si>
-    <t>LFSB Basel-Mulhouse-Freiburg EuroAirport</t>
-  </si>
-  <si>
-    <t>francevfr-airport-lfst-strasbourg</t>
-  </si>
-  <si>
-    <t>LFST</t>
-  </si>
-  <si>
-    <t>1.3.3</t>
-  </si>
-  <si>
-    <t>LFST Strasbourg-Entzheim Airport</t>
-  </si>
-  <si>
-    <t>pilotexperiencesim-airport-lftz-st-tropez</t>
-  </si>
-  <si>
-    <t>LFTZ</t>
-  </si>
-  <si>
-    <t>LFTZ Saint Tropez</t>
-  </si>
-  <si>
-    <t>GIBRALTAR (0 / 1)</t>
   </si>
   <si>
     <t>GRECE (0 / 8)</t>
@@ -3173,7 +3179,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6911,144 +6917,144 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>93</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="257175" cy="161925"/>
+    <xdr:ext cx="257175" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="161" name="Picture 160"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1609725" cy="171450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="162" name="Picture 161"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="257175" cy="190500"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="162" name="Picture 161"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1609725" cy="171450"/>
+    <xdr:ext cx="257175" cy="161925"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="163" name="Picture 162"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>95</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="257175" cy="161925"/>
+    <xdr:ext cx="257175" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="164" name="Picture 163"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1609725" cy="171450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="165" name="Picture 164"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>96</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="257175" cy="190500"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="165" name="Picture 164"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect"/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1609725" cy="171450"/>
+    <xdr:ext cx="257175" cy="161925"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="166" name="Picture 165"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7198,7 +7204,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7248,7 +7254,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -16838,7 +16844,7 @@
         <v>34</v>
       </c>
       <c t="s" r="X9" s="2">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
@@ -16850,10 +16856,10 @@
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c t="s" r="F10" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c t="s" r="G10" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="9"/>
@@ -16862,10 +16868,10 @@
       </c>
       <c r="K10" s="3"/>
       <c t="s" r="L10" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c t="s" r="M10" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N10" s="5"/>
       <c r="O10" s="3"/>
@@ -16903,7 +16909,7 @@
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c t="s" r="E11" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -16940,22 +16946,22 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c t="s" r="F12" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c t="s" r="G12" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="9"/>
       <c t="s" r="J12" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K12" s="3"/>
       <c t="s" r="L12" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="M12" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="3"/>
@@ -16991,7 +16997,7 @@
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c t="s" r="E13" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -17028,22 +17034,22 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c t="s" r="F14" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c t="s" r="G14" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="9"/>
       <c t="s" r="J14" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K14" s="3"/>
       <c t="s" r="L14" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c t="s" r="M14" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="3"/>
@@ -17068,7 +17074,7 @@
         <v>34</v>
       </c>
       <c t="s" r="X14" s="2">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
@@ -17352,7 +17358,7 @@
       <c r="H21" s="3"/>
       <c r="I21" s="9"/>
       <c t="s" r="J21" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K21" s="3"/>
       <c t="s" r="L21" s="2">
@@ -17668,7 +17674,7 @@
       <c r="H28" s="3"/>
       <c r="I28" s="9"/>
       <c t="s" r="J28" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K28" s="3"/>
       <c t="s" r="L28" s="2">
@@ -19256,7 +19262,7 @@
       <c t="s" r="J60" s="2">
         <v>98</v>
       </c>
-      <c r="K60" s="2"/>
+      <c r="K60" s="3"/>
       <c t="s" r="L60" s="2">
         <v>213</v>
       </c>
@@ -19264,7 +19270,7 @@
         <v>214</v>
       </c>
       <c r="N60" s="5"/>
-      <c r="O60" s="2"/>
+      <c r="O60" s="3"/>
       <c t="s" r="P60" s="5">
         <v>23</v>
       </c>
@@ -19468,7 +19474,7 @@
       </c>
       <c r="I64" s="9"/>
       <c t="s" r="J64" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K64" s="3"/>
       <c t="s" r="L64" s="2">
@@ -19883,7 +19889,7 @@
         <v>260</v>
       </c>
       <c t="s" r="M72" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N72" s="5"/>
       <c r="O72" s="3"/>
@@ -19937,7 +19943,7 @@
         <v>263</v>
       </c>
       <c t="s" r="M73" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N73" s="5"/>
       <c r="O73" s="3"/>
@@ -20290,7 +20296,7 @@
       <c r="H80" s="3"/>
       <c r="I80" s="9"/>
       <c t="s" r="J80" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K80" s="3"/>
       <c t="s" r="L80" s="2">
@@ -20722,14 +20728,14 @@
       <c r="H89" s="3"/>
       <c r="I89" s="9"/>
       <c t="s" r="J89" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K89" s="3"/>
       <c t="s" r="L89" s="2">
         <v>309</v>
       </c>
       <c t="s" r="M89" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N89" s="5"/>
       <c r="O89" s="3"/>
@@ -20804,15 +20810,11 @@
       <c t="s" r="F91" s="2">
         <v>311</v>
       </c>
-      <c t="s" r="G91" s="2">
-        <v>312</v>
-      </c>
-      <c t="s" r="H91" s="2">
-        <v>312</v>
-      </c>
+      <c r="G91" s="2"/>
+      <c r="H91" s="3"/>
       <c r="I91" s="9"/>
       <c t="s" r="J91" s="2">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="K91" s="3"/>
       <c t="s" r="L91" s="2">
@@ -20859,21 +20861,21 @@
         <v>314</v>
       </c>
       <c t="s" r="G92" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c t="s" r="H92" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="I92" s="9"/>
       <c t="s" r="J92" s="2">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="K92" s="3"/>
       <c t="s" r="L92" s="2">
         <v>315</v>
       </c>
       <c t="s" r="M92" s="2">
-        <v>41</v>
+        <v>313</v>
       </c>
       <c r="N92" s="5"/>
       <c r="O92" s="3"/>
@@ -20913,19 +20915,21 @@
         <v>316</v>
       </c>
       <c t="s" r="G93" s="2">
-        <v>317</v>
-      </c>
-      <c r="H93" s="3"/>
+        <v>315</v>
+      </c>
+      <c t="s" r="H93" s="2">
+        <v>315</v>
+      </c>
       <c r="I93" s="9"/>
       <c t="s" r="J93" s="2">
-        <v>318</v>
+        <v>55</v>
       </c>
       <c r="K93" s="3"/>
       <c t="s" r="L93" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c t="s" r="M93" s="2">
-        <v>320</v>
+        <v>41</v>
       </c>
       <c r="N93" s="5"/>
       <c r="O93" s="3"/>
@@ -20956,183 +20960,181 @@
       <c r="Z93" s="2"/>
       <c r="AA93" s="2"/>
     </row>
-    <row r="94" ht="12.75" customHeight="1">
+    <row r="94" ht="15" customHeight="1">
       <c r="A94" s="8"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
-      <c t="s" r="E94" s="2">
+      <c r="D94" s="8"/>
+      <c t="s" r="F94" s="2">
+        <v>318</v>
+      </c>
+      <c t="s" r="G94" s="2">
+        <v>319</v>
+      </c>
+      <c r="H94" s="3"/>
+      <c r="I94" s="9"/>
+      <c t="s" r="J94" s="2">
+        <v>320</v>
+      </c>
+      <c r="K94" s="3"/>
+      <c t="s" r="L94" s="2">
         <v>321</v>
       </c>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="3"/>
-      <c r="I94" s="4"/>
-      <c r="J94" s="3"/>
-      <c r="K94" s="3"/>
-      <c r="L94" s="3"/>
-      <c r="M94" s="3"/>
+      <c t="s" r="M94" s="2">
+        <v>322</v>
+      </c>
       <c r="N94" s="5"/>
       <c r="O94" s="3"/>
       <c t="s" r="P94" s="5">
         <v>23</v>
       </c>
-      <c r="Q94" s="6"/>
-      <c r="R94" s="6"/>
+      <c r="Q94" s="10"/>
+      <c r="R94" s="10"/>
       <c r="S94" s="7">
         <v>0</v>
       </c>
       <c r="T94" s="7">
         <v>0</v>
       </c>
-      <c r="U94" s="3"/>
-      <c r="V94" s="2"/>
-      <c r="W94" s="6"/>
-      <c r="X94" s="2"/>
+      <c t="s" r="U94" s="2">
+        <v>32</v>
+      </c>
+      <c t="s" r="V94" s="2">
+        <v>33</v>
+      </c>
+      <c t="s" r="W94" s="3">
+        <v>34</v>
+      </c>
+      <c t="s" r="X94" s="2">
+        <v>35</v>
+      </c>
       <c r="Y94" s="2"/>
       <c r="Z94" s="2"/>
       <c r="AA94" s="2"/>
     </row>
-    <row r="95" ht="15" customHeight="1">
+    <row r="95" ht="12.75" customHeight="1">
       <c r="A95" s="8"/>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
-      <c t="s" r="F95" s="2">
-        <v>322</v>
-      </c>
-      <c t="s" r="G95" s="2">
+      <c t="s" r="E95" s="2">
         <v>323</v>
       </c>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
       <c r="H95" s="3"/>
-      <c r="I95" s="9"/>
-      <c t="s" r="J95" s="2">
-        <v>324</v>
-      </c>
+      <c r="I95" s="4"/>
+      <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-      <c t="s" r="L95" s="2">
-        <v>325</v>
-      </c>
-      <c t="s" r="M95" s="2">
-        <v>326</v>
-      </c>
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
       <c r="N95" s="5"/>
       <c r="O95" s="3"/>
       <c t="s" r="P95" s="5">
         <v>23</v>
       </c>
-      <c r="Q95" s="10"/>
-      <c r="R95" s="10"/>
+      <c r="Q95" s="6"/>
+      <c r="R95" s="6"/>
       <c r="S95" s="7">
         <v>0</v>
       </c>
       <c r="T95" s="7">
         <v>0</v>
       </c>
-      <c t="s" r="U95" s="2">
-        <v>32</v>
-      </c>
-      <c t="s" r="V95" s="2">
-        <v>33</v>
-      </c>
-      <c t="s" r="W95" s="3">
-        <v>34</v>
-      </c>
-      <c t="s" r="X95" s="2">
-        <v>35</v>
-      </c>
+      <c r="U95" s="3"/>
+      <c r="V95" s="2"/>
+      <c r="W95" s="6"/>
+      <c r="X95" s="2"/>
       <c r="Y95" s="2"/>
       <c r="Z95" s="2"/>
       <c r="AA95" s="2"/>
     </row>
-    <row r="96" ht="12.75" customHeight="1">
+    <row r="96" ht="15" customHeight="1">
       <c r="A96" s="8"/>
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
-      <c t="s" r="E96" s="2">
+      <c r="D96" s="8"/>
+      <c t="s" r="F96" s="2">
+        <v>324</v>
+      </c>
+      <c t="s" r="G96" s="2">
+        <v>325</v>
+      </c>
+      <c r="H96" s="3"/>
+      <c r="I96" s="9"/>
+      <c t="s" r="J96" s="2">
+        <v>326</v>
+      </c>
+      <c r="K96" s="3"/>
+      <c t="s" r="L96" s="2">
         <v>327</v>
       </c>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="3"/>
-      <c r="I96" s="4"/>
-      <c r="J96" s="3"/>
-      <c r="K96" s="3"/>
-      <c r="L96" s="3"/>
-      <c r="M96" s="3"/>
+      <c t="s" r="M96" s="2">
+        <v>328</v>
+      </c>
       <c r="N96" s="5"/>
       <c r="O96" s="3"/>
       <c t="s" r="P96" s="5">
         <v>23</v>
       </c>
-      <c r="Q96" s="6"/>
-      <c r="R96" s="6"/>
+      <c r="Q96" s="10"/>
+      <c r="R96" s="10"/>
       <c r="S96" s="7">
         <v>0</v>
       </c>
       <c r="T96" s="7">
         <v>0</v>
       </c>
-      <c r="U96" s="3"/>
-      <c r="V96" s="2"/>
-      <c r="W96" s="6"/>
-      <c r="X96" s="2"/>
+      <c t="s" r="U96" s="2">
+        <v>32</v>
+      </c>
+      <c t="s" r="V96" s="2">
+        <v>33</v>
+      </c>
+      <c t="s" r="W96" s="3">
+        <v>34</v>
+      </c>
+      <c t="s" r="X96" s="2">
+        <v>35</v>
+      </c>
       <c r="Y96" s="2"/>
       <c r="Z96" s="2"/>
       <c r="AA96" s="2"/>
     </row>
-    <row r="97" ht="15" customHeight="1">
+    <row r="97" ht="12.75" customHeight="1">
       <c r="A97" s="8"/>
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
-      <c t="s" r="F97" s="2">
-        <v>328</v>
-      </c>
-      <c t="s" r="G97" s="2">
+      <c t="s" r="E97" s="2">
         <v>329</v>
       </c>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
       <c r="H97" s="3"/>
-      <c r="I97" s="9"/>
-      <c t="s" r="J97" s="2">
-        <v>139</v>
-      </c>
+      <c r="I97" s="4"/>
+      <c r="J97" s="3"/>
       <c r="K97" s="3"/>
-      <c t="s" r="L97" s="2">
-        <v>328</v>
-      </c>
-      <c t="s" r="M97" s="2">
-        <v>85</v>
-      </c>
+      <c r="L97" s="3"/>
+      <c r="M97" s="3"/>
       <c r="N97" s="5"/>
       <c r="O97" s="3"/>
       <c t="s" r="P97" s="5">
         <v>23</v>
       </c>
-      <c r="Q97" s="10"/>
-      <c r="R97" s="10"/>
+      <c r="Q97" s="6"/>
+      <c r="R97" s="6"/>
       <c r="S97" s="7">
         <v>0</v>
       </c>
       <c r="T97" s="7">
         <v>0</v>
       </c>
-      <c t="s" r="U97" s="2">
-        <v>32</v>
-      </c>
-      <c t="s" r="V97" s="2">
-        <v>33</v>
-      </c>
-      <c t="s" r="W97" s="3">
-        <v>34</v>
-      </c>
-      <c t="s" r="X97" s="2">
-        <v>35</v>
-      </c>
+      <c r="U97" s="3"/>
+      <c r="V97" s="2"/>
+      <c r="W97" s="6"/>
+      <c r="X97" s="2"/>
       <c r="Y97" s="2"/>
       <c r="Z97" s="2"/>
-      <c t="s" r="AA97" s="2">
-        <v>330</v>
-      </c>
+      <c r="AA97" s="2"/>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="8"/>
@@ -21140,19 +21142,19 @@
       <c r="C98" s="8"/>
       <c r="D98" s="8"/>
       <c t="s" r="F98" s="2">
+        <v>330</v>
+      </c>
+      <c t="s" r="G98" s="2">
         <v>331</v>
-      </c>
-      <c t="s" r="G98" s="2">
-        <v>332</v>
       </c>
       <c r="H98" s="3"/>
       <c r="I98" s="9"/>
       <c t="s" r="J98" s="2">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="K98" s="3"/>
       <c t="s" r="L98" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c t="s" r="M98" s="2">
         <v>85</v>
@@ -21185,7 +21187,7 @@
       <c r="Y98" s="2"/>
       <c r="Z98" s="2"/>
       <c t="s" r="AA98" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
@@ -21194,19 +21196,19 @@
       <c r="C99" s="8"/>
       <c r="D99" s="8"/>
       <c t="s" r="F99" s="2">
+        <v>333</v>
+      </c>
+      <c t="s" r="G99" s="2">
         <v>334</v>
-      </c>
-      <c t="s" r="G99" s="2">
-        <v>335</v>
       </c>
       <c r="H99" s="3"/>
       <c r="I99" s="9"/>
       <c t="s" r="J99" s="2">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="K99" s="3"/>
       <c t="s" r="L99" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c t="s" r="M99" s="2">
         <v>85</v>
@@ -21239,7 +21241,7 @@
       <c r="Y99" s="2"/>
       <c r="Z99" s="2"/>
       <c t="s" r="AA99" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -21248,22 +21250,22 @@
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
       <c t="s" r="F100" s="2">
+        <v>336</v>
+      </c>
+      <c t="s" r="G100" s="2">
         <v>337</v>
-      </c>
-      <c t="s" r="G100" s="2">
-        <v>338</v>
       </c>
       <c r="H100" s="3"/>
       <c r="I100" s="9"/>
       <c t="s" r="J100" s="2">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="K100" s="3"/>
       <c t="s" r="L100" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c t="s" r="M100" s="2">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="N100" s="5"/>
       <c r="O100" s="3"/>
@@ -21293,7 +21295,7 @@
       <c r="Y100" s="2"/>
       <c r="Z100" s="2"/>
       <c t="s" r="AA100" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
@@ -21302,22 +21304,22 @@
       <c r="C101" s="8"/>
       <c r="D101" s="8"/>
       <c t="s" r="F101" s="2">
+        <v>339</v>
+      </c>
+      <c t="s" r="G101" s="2">
         <v>340</v>
-      </c>
-      <c t="s" r="G101" s="2">
-        <v>341</v>
       </c>
       <c r="H101" s="3"/>
       <c r="I101" s="9"/>
       <c t="s" r="J101" s="2">
-        <v>342</v>
+        <v>55</v>
       </c>
       <c r="K101" s="3"/>
       <c t="s" r="L101" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c t="s" r="M101" s="2">
-        <v>344</v>
+        <v>41</v>
       </c>
       <c r="N101" s="5"/>
       <c r="O101" s="3"/>
@@ -21346,7 +21348,9 @@
       </c>
       <c r="Y101" s="2"/>
       <c r="Z101" s="2"/>
-      <c r="AA101" s="2"/>
+      <c t="s" r="AA101" s="2">
+        <v>332</v>
+      </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="8"/>
@@ -21354,22 +21358,22 @@
       <c r="C102" s="8"/>
       <c r="D102" s="8"/>
       <c t="s" r="F102" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c t="s" r="G102" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H102" s="3"/>
       <c r="I102" s="9"/>
       <c t="s" r="J102" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="K102" s="3"/>
       <c t="s" r="L102" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c t="s" r="M102" s="2">
-        <v>85</v>
+        <v>346</v>
       </c>
       <c r="N102" s="5"/>
       <c r="O102" s="3"/>
@@ -21398,9 +21402,7 @@
       </c>
       <c r="Y102" s="2"/>
       <c r="Z102" s="2"/>
-      <c t="s" r="AA102" s="2">
-        <v>330</v>
-      </c>
+      <c r="AA102" s="2"/>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="8"/>
@@ -21408,22 +21410,22 @@
       <c r="C103" s="8"/>
       <c r="D103" s="8"/>
       <c t="s" r="F103" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c t="s" r="G103" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" s="9"/>
       <c t="s" r="J103" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K103" s="3"/>
       <c t="s" r="L103" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c t="s" r="M103" s="2">
-        <v>353</v>
+        <v>85</v>
       </c>
       <c r="N103" s="5"/>
       <c r="O103" s="3"/>
@@ -21452,7 +21454,9 @@
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" s="2"/>
-      <c r="AA103" s="2"/>
+      <c t="s" r="AA103" s="2">
+        <v>332</v>
+      </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="8"/>
@@ -21460,22 +21464,22 @@
       <c r="C104" s="8"/>
       <c r="D104" s="8"/>
       <c t="s" r="F104" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c t="s" r="G104" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H104" s="3"/>
       <c r="I104" s="9"/>
       <c t="s" r="J104" s="2">
-        <v>72</v>
+        <v>353</v>
       </c>
       <c r="K104" s="3"/>
       <c t="s" r="L104" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c t="s" r="M104" s="2">
-        <v>275</v>
+        <v>355</v>
       </c>
       <c r="N104" s="5"/>
       <c r="O104" s="3"/>
@@ -21504,9 +21508,7 @@
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" s="2"/>
-      <c t="s" r="AA104" s="2">
-        <v>330</v>
-      </c>
+      <c r="AA104" s="2"/>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="8"/>
@@ -21514,22 +21516,22 @@
       <c r="C105" s="8"/>
       <c r="D105" s="8"/>
       <c t="s" r="F105" s="2">
+        <v>356</v>
+      </c>
+      <c t="s" r="G105" s="2">
         <v>357</v>
-      </c>
-      <c t="s" r="G105" s="2">
-        <v>358</v>
       </c>
       <c r="H105" s="3"/>
       <c r="I105" s="9"/>
       <c t="s" r="J105" s="2">
-        <v>139</v>
+        <v>72</v>
       </c>
       <c r="K105" s="3"/>
       <c t="s" r="L105" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c t="s" r="M105" s="2">
-        <v>85</v>
+        <v>275</v>
       </c>
       <c r="N105" s="5"/>
       <c r="O105" s="3"/>
@@ -21559,7 +21561,7 @@
       <c r="Y105" s="2"/>
       <c r="Z105" s="2"/>
       <c t="s" r="AA105" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
@@ -21568,24 +21570,22 @@
       <c r="C106" s="8"/>
       <c r="D106" s="8"/>
       <c t="s" r="F106" s="2">
+        <v>359</v>
+      </c>
+      <c t="s" r="G106" s="2">
         <v>360</v>
       </c>
-      <c t="s" r="G106" s="2">
-        <v>361</v>
-      </c>
-      <c t="s" r="H106" s="2">
-        <v>361</v>
-      </c>
+      <c r="H106" s="3"/>
       <c r="I106" s="9"/>
       <c t="s" r="J106" s="2">
-        <v>259</v>
+        <v>139</v>
       </c>
       <c r="K106" s="3"/>
       <c t="s" r="L106" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c t="s" r="M106" s="2">
-        <v>294</v>
+        <v>85</v>
       </c>
       <c r="N106" s="5"/>
       <c r="O106" s="3"/>
@@ -21613,11 +21613,9 @@
         <v>35</v>
       </c>
       <c r="Y106" s="2"/>
-      <c t="s" r="Z106" s="2">
-        <v>63</v>
-      </c>
+      <c r="Z106" s="2"/>
       <c t="s" r="AA106" s="2">
-        <v>363</v>
+        <v>332</v>
       </c>
     </row>
     <row r="107" ht="12.75" customHeight="1">
@@ -21625,7 +21623,7 @@
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
       <c t="s" r="E107" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -21662,10 +21660,10 @@
       <c r="C108" s="8"/>
       <c r="D108" s="8"/>
       <c t="s" r="F108" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c t="s" r="G108" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H108" s="3"/>
       <c r="I108" s="9"/>
@@ -21674,10 +21672,10 @@
       </c>
       <c r="K108" s="3"/>
       <c t="s" r="L108" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c t="s" r="M108" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="N108" s="5"/>
       <c r="O108" s="3"/>
@@ -21713,7 +21711,7 @@
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
       <c t="s" r="E109" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
@@ -21750,10 +21748,10 @@
       <c r="C110" s="8"/>
       <c r="D110" s="8"/>
       <c t="s" r="F110" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c t="s" r="G110" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H110" s="3"/>
       <c r="I110" s="9"/>
@@ -21762,7 +21760,7 @@
       </c>
       <c r="K110" s="3"/>
       <c t="s" r="L110" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c t="s" r="M110" s="2">
         <v>85</v>
@@ -21795,7 +21793,7 @@
       <c r="Y110" s="2"/>
       <c r="Z110" s="2"/>
       <c t="s" r="AA110" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1">
@@ -21804,19 +21802,19 @@
       <c r="C111" s="8"/>
       <c r="D111" s="8"/>
       <c t="s" r="F111" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c t="s" r="G111" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H111" s="3"/>
       <c r="I111" s="9"/>
       <c t="s" r="J111" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="K111" s="3"/>
       <c t="s" r="L111" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c t="s" r="M111" s="2">
         <v>275</v>
@@ -21849,7 +21847,7 @@
       <c r="Y111" s="2"/>
       <c r="Z111" s="2"/>
       <c t="s" r="AA111" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="112" ht="12.75" customHeight="1">
@@ -21857,7 +21855,7 @@
       <c r="B112" s="8"/>
       <c r="C112" s="8"/>
       <c t="s" r="E112" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
@@ -21894,22 +21892,22 @@
       <c r="C113" s="8"/>
       <c r="D113" s="8"/>
       <c t="s" r="F113" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c t="s" r="G113" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H113" s="3"/>
       <c r="I113" s="9"/>
       <c t="s" r="J113" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K113" s="3"/>
       <c t="s" r="L113" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c t="s" r="M113" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="N113" s="5"/>
       <c r="O113" s="3"/>
@@ -21939,7 +21937,7 @@
       <c r="Y113" s="2"/>
       <c r="Z113" s="2"/>
       <c t="s" r="AA113" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1">
@@ -21948,10 +21946,10 @@
       <c r="C114" s="8"/>
       <c r="D114" s="8"/>
       <c t="s" r="F114" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c t="s" r="G114" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H114" s="3"/>
       <c r="I114" s="9"/>
@@ -21960,10 +21958,10 @@
       </c>
       <c r="K114" s="3"/>
       <c t="s" r="L114" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c t="s" r="M114" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="N114" s="5"/>
       <c r="O114" s="3"/>
@@ -21993,7 +21991,7 @@
       <c r="Y114" s="2"/>
       <c r="Z114" s="2"/>
       <c t="s" r="AA114" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -22002,10 +22000,10 @@
       <c r="C115" s="8"/>
       <c r="D115" s="8"/>
       <c t="s" r="F115" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c t="s" r="G115" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H115" s="3"/>
       <c r="I115" s="9"/>
@@ -22014,10 +22012,10 @@
       </c>
       <c r="K115" s="3"/>
       <c t="s" r="L115" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c t="s" r="M115" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N115" s="5"/>
       <c r="O115" s="3"/>
@@ -22047,7 +22045,7 @@
       <c r="Y115" s="2"/>
       <c r="Z115" s="2"/>
       <c t="s" r="AA115" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1">
@@ -22056,10 +22054,10 @@
       <c r="C116" s="8"/>
       <c r="D116" s="8"/>
       <c t="s" r="F116" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c t="s" r="G116" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H116" s="3"/>
       <c r="I116" s="9"/>
@@ -22068,10 +22066,10 @@
       </c>
       <c r="K116" s="3"/>
       <c t="s" r="L116" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c t="s" r="M116" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N116" s="5"/>
       <c r="O116" s="3"/>
@@ -22108,13 +22106,13 @@
       <c r="C117" s="8"/>
       <c r="D117" s="8"/>
       <c t="s" r="F117" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c t="s" r="G117" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c t="s" r="H117" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="I117" s="9"/>
       <c t="s" r="J117" s="2">
@@ -22122,10 +22120,10 @@
       </c>
       <c r="K117" s="3"/>
       <c t="s" r="L117" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c t="s" r="M117" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N117" s="5"/>
       <c r="O117" s="3"/>
@@ -22162,24 +22160,24 @@
       <c r="C118" s="8"/>
       <c r="D118" s="8"/>
       <c t="s" r="F118" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c t="s" r="G118" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c t="s" r="H118" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="I118" s="9"/>
       <c t="s" r="J118" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K118" s="3"/>
       <c t="s" r="L118" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c t="s" r="M118" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="N118" s="5"/>
       <c r="O118" s="3"/>
@@ -22209,7 +22207,7 @@
       <c r="Y118" s="2"/>
       <c r="Z118" s="2"/>
       <c t="s" r="AA118" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1">
@@ -22218,13 +22216,13 @@
       <c r="C119" s="8"/>
       <c r="D119" s="8"/>
       <c t="s" r="F119" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c t="s" r="G119" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c t="s" r="H119" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="I119" s="9"/>
       <c t="s" r="J119" s="2">
@@ -22232,10 +22230,10 @@
       </c>
       <c r="K119" s="3"/>
       <c t="s" r="L119" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c t="s" r="M119" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="N119" s="5"/>
       <c r="O119" s="3"/>
@@ -22265,7 +22263,7 @@
       <c r="Y119" s="2"/>
       <c r="Z119" s="2"/>
       <c t="s" r="AA119" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -22274,10 +22272,10 @@
       <c r="C120" s="8"/>
       <c r="D120" s="8"/>
       <c t="s" r="F120" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c t="s" r="G120" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H120" s="3"/>
       <c r="I120" s="9"/>
@@ -22286,10 +22284,10 @@
       </c>
       <c r="K120" s="3"/>
       <c t="s" r="L120" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c t="s" r="M120" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N120" s="5"/>
       <c r="O120" s="3"/>
@@ -22326,13 +22324,13 @@
       <c r="C121" s="8"/>
       <c r="D121" s="8"/>
       <c t="s" r="F121" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c t="s" r="G121" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c t="s" r="H121" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I121" s="9"/>
       <c t="s" r="J121" s="2">
@@ -22340,10 +22338,10 @@
       </c>
       <c r="K121" s="3"/>
       <c t="s" r="L121" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c t="s" r="M121" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N121" s="5"/>
       <c r="O121" s="3"/>
@@ -22380,13 +22378,13 @@
       <c r="C122" s="8"/>
       <c r="D122" s="8"/>
       <c t="s" r="F122" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c t="s" r="G122" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c t="s" r="H122" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I122" s="9"/>
       <c t="s" r="J122" s="2">
@@ -22394,10 +22392,10 @@
       </c>
       <c r="K122" s="3"/>
       <c t="s" r="L122" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c t="s" r="M122" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="N122" s="5"/>
       <c r="O122" s="3"/>
@@ -22427,7 +22425,7 @@
       <c r="Y122" s="2"/>
       <c r="Z122" s="2"/>
       <c t="s" r="AA122" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1">
@@ -22436,10 +22434,10 @@
       <c r="C123" s="8"/>
       <c r="D123" s="8"/>
       <c t="s" r="F123" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c t="s" r="G123" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H123" s="3"/>
       <c r="I123" s="9"/>
@@ -22448,10 +22446,10 @@
       </c>
       <c r="K123" s="3"/>
       <c t="s" r="L123" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c t="s" r="M123" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="N123" s="5"/>
       <c r="O123" s="3"/>
@@ -22488,13 +22486,13 @@
       <c r="C124" s="8"/>
       <c r="D124" s="8"/>
       <c t="s" r="F124" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c t="s" r="G124" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c t="s" r="H124" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I124" s="9"/>
       <c t="s" r="J124" s="2">
@@ -22502,10 +22500,10 @@
       </c>
       <c r="K124" s="3"/>
       <c t="s" r="L124" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c t="s" r="M124" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N124" s="5"/>
       <c r="O124" s="3"/>
@@ -22542,13 +22540,13 @@
       <c r="C125" s="8"/>
       <c r="D125" s="8"/>
       <c t="s" r="F125" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c t="s" r="G125" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c t="s" r="H125" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I125" s="9"/>
       <c t="s" r="J125" s="2">
@@ -22556,7 +22554,7 @@
       </c>
       <c r="K125" s="3"/>
       <c t="s" r="L125" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c t="s" r="M125" s="2">
         <v>201</v>
@@ -22596,10 +22594,10 @@
       <c r="C126" s="8"/>
       <c r="D126" s="8"/>
       <c t="s" r="F126" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c t="s" r="G126" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H126" s="3"/>
       <c r="I126" s="9"/>
@@ -22608,10 +22606,10 @@
       </c>
       <c r="K126" s="3"/>
       <c t="s" r="L126" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c t="s" r="M126" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="N126" s="5"/>
       <c r="O126" s="3"/>
@@ -22641,7 +22639,7 @@
       <c r="Y126" s="2"/>
       <c r="Z126" s="2"/>
       <c t="s" r="AA126" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1">
@@ -22650,10 +22648,10 @@
       <c r="C127" s="8"/>
       <c r="D127" s="8"/>
       <c t="s" r="F127" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c t="s" r="G127" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H127" s="3"/>
       <c r="I127" s="9"/>
@@ -22662,7 +22660,7 @@
       </c>
       <c r="K127" s="3"/>
       <c t="s" r="L127" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c t="s" r="M127" s="2">
         <v>294</v>
@@ -22695,7 +22693,7 @@
       <c r="Y127" s="2"/>
       <c r="Z127" s="2"/>
       <c t="s" r="AA127" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1">
@@ -22704,24 +22702,24 @@
       <c r="C128" s="8"/>
       <c r="D128" s="8"/>
       <c t="s" r="F128" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c t="s" r="G128" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c t="s" r="H128" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I128" s="9"/>
       <c t="s" r="J128" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="K128" s="3"/>
       <c t="s" r="L128" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c t="s" r="M128" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="N128" s="5"/>
       <c r="O128" s="3"/>
@@ -22746,7 +22744,7 @@
         <v>34</v>
       </c>
       <c t="s" r="X128" s="2">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" s="2"/>
@@ -22758,13 +22756,13 @@
       <c r="C129" s="8"/>
       <c r="D129" s="8"/>
       <c t="s" r="F129" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c t="s" r="G129" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c t="s" r="H129" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I129" s="9"/>
       <c t="s" r="J129" s="2">
@@ -22772,10 +22770,10 @@
       </c>
       <c r="K129" s="3"/>
       <c t="s" r="L129" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c t="s" r="M129" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="N129" s="5"/>
       <c r="O129" s="3"/>
@@ -22805,7 +22803,7 @@
       <c r="Y129" s="2"/>
       <c r="Z129" s="2"/>
       <c t="s" r="AA129" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -22814,22 +22812,22 @@
       <c r="C130" s="8"/>
       <c r="D130" s="8"/>
       <c t="s" r="F130" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c t="s" r="G130" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H130" s="3"/>
       <c r="I130" s="9"/>
       <c t="s" r="J130" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K130" s="3"/>
       <c t="s" r="L130" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c t="s" r="M130" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="N130" s="5"/>
       <c r="O130" s="3"/>
@@ -22859,7 +22857,7 @@
       <c r="Y130" s="2"/>
       <c r="Z130" s="2"/>
       <c t="s" r="AA130" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1">
@@ -22868,10 +22866,10 @@
       <c r="C131" s="8"/>
       <c r="D131" s="8"/>
       <c t="s" r="F131" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c t="s" r="G131" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H131" s="3"/>
       <c r="I131" s="9"/>
@@ -22880,10 +22878,10 @@
       </c>
       <c r="K131" s="3"/>
       <c t="s" r="L131" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c t="s" r="M131" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="N131" s="5"/>
       <c r="O131" s="3"/>
@@ -22913,7 +22911,7 @@
       <c r="Y131" s="2"/>
       <c r="Z131" s="2"/>
       <c t="s" r="AA131" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1">
@@ -22922,13 +22920,13 @@
       <c r="C132" s="8"/>
       <c r="D132" s="8"/>
       <c t="s" r="F132" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c t="s" r="G132" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c t="s" r="H132" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="I132" s="9"/>
       <c t="s" r="J132" s="2">
@@ -22936,10 +22934,10 @@
       </c>
       <c r="K132" s="3"/>
       <c t="s" r="L132" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c t="s" r="M132" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="N132" s="5"/>
       <c r="O132" s="3"/>
@@ -22976,13 +22974,13 @@
       <c r="C133" s="8"/>
       <c r="D133" s="8"/>
       <c t="s" r="F133" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c t="s" r="G133" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c t="s" r="H133" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="I133" s="9"/>
       <c t="s" r="J133" s="2">
@@ -22990,10 +22988,10 @@
       </c>
       <c r="K133" s="3"/>
       <c t="s" r="L133" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c t="s" r="M133" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="N133" s="5"/>
       <c r="O133" s="3"/>
@@ -23030,10 +23028,10 @@
       <c r="C134" s="8"/>
       <c r="D134" s="8"/>
       <c t="s" r="F134" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c t="s" r="G134" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="H134" s="3"/>
       <c r="I134" s="9"/>
@@ -23042,10 +23040,10 @@
       </c>
       <c r="K134" s="3"/>
       <c t="s" r="L134" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c t="s" r="M134" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N134" s="5"/>
       <c r="O134" s="3"/>
@@ -23075,7 +23073,7 @@
       <c r="Y134" s="2"/>
       <c r="Z134" s="2"/>
       <c t="s" r="AA134" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -23084,10 +23082,10 @@
       <c r="C135" s="8"/>
       <c r="D135" s="8"/>
       <c t="s" r="F135" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c t="s" r="G135" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H135" s="3"/>
       <c r="I135" s="9"/>
@@ -23096,10 +23094,10 @@
       </c>
       <c r="K135" s="3"/>
       <c t="s" r="L135" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c t="s" r="M135" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N135" s="5"/>
       <c r="O135" s="3"/>
@@ -23129,7 +23127,7 @@
       <c r="Y135" s="2"/>
       <c r="Z135" s="2"/>
       <c t="s" r="AA135" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1">
@@ -23138,10 +23136,10 @@
       <c r="C136" s="8"/>
       <c r="D136" s="8"/>
       <c t="s" r="F136" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c t="s" r="G136" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H136" s="3"/>
       <c r="I136" s="9"/>
@@ -23150,10 +23148,10 @@
       </c>
       <c r="K136" s="3"/>
       <c t="s" r="L136" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c t="s" r="M136" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N136" s="5"/>
       <c r="O136" s="3"/>
@@ -23183,7 +23181,7 @@
       <c r="Y136" s="2"/>
       <c r="Z136" s="2"/>
       <c t="s" r="AA136" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1">
@@ -23192,10 +23190,10 @@
       <c r="C137" s="8"/>
       <c r="D137" s="8"/>
       <c t="s" r="F137" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c t="s" r="G137" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H137" s="3"/>
       <c r="I137" s="9"/>
@@ -23204,10 +23202,10 @@
       </c>
       <c r="K137" s="3"/>
       <c t="s" r="L137" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c t="s" r="M137" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N137" s="5"/>
       <c r="O137" s="3"/>
@@ -23237,7 +23235,7 @@
       <c r="Y137" s="2"/>
       <c r="Z137" s="2"/>
       <c t="s" r="AA137" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1">
@@ -23246,22 +23244,22 @@
       <c r="C138" s="8"/>
       <c r="D138" s="8"/>
       <c t="s" r="F138" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c t="s" r="G138" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H138" s="3"/>
       <c r="I138" s="9"/>
       <c t="s" r="J138" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K138" s="3"/>
       <c t="s" r="L138" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c t="s" r="M138" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N138" s="5"/>
       <c r="O138" s="3"/>
@@ -23291,7 +23289,7 @@
       <c r="Y138" s="2"/>
       <c r="Z138" s="2"/>
       <c t="s" r="AA138" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1">
@@ -23300,10 +23298,10 @@
       <c r="C139" s="8"/>
       <c r="D139" s="8"/>
       <c t="s" r="F139" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c t="s" r="G139" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H139" s="3"/>
       <c r="I139" s="9"/>
@@ -23312,10 +23310,10 @@
       </c>
       <c r="K139" s="3"/>
       <c t="s" r="L139" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c t="s" r="M139" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="N139" s="5"/>
       <c r="O139" s="3"/>
@@ -23345,7 +23343,7 @@
       <c r="Y139" s="2"/>
       <c r="Z139" s="2"/>
       <c t="s" r="AA139" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="140" ht="12.75" customHeight="1">
@@ -23353,7 +23351,7 @@
       <c r="B140" s="8"/>
       <c r="C140" s="8"/>
       <c t="s" r="E140" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
@@ -23390,21 +23388,19 @@
       <c r="C141" s="8"/>
       <c r="D141" s="8"/>
       <c t="s" r="F141" s="2">
-        <v>360</v>
+        <v>466</v>
       </c>
       <c t="s" r="G141" s="2">
-        <v>361</v>
-      </c>
-      <c t="s" r="H141" s="2">
-        <v>361</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="H141" s="3"/>
       <c r="I141" s="9"/>
       <c t="s" r="J141" s="2">
         <v>259</v>
       </c>
       <c r="K141" s="3"/>
       <c t="s" r="L141" s="2">
-        <v>362</v>
+        <v>468</v>
       </c>
       <c t="s" r="M141" s="2">
         <v>294</v>
@@ -23435,11 +23431,9 @@
         <v>35</v>
       </c>
       <c r="Y141" s="2"/>
-      <c t="s" r="Z141" s="2">
-        <v>63</v>
-      </c>
+      <c r="Z141" s="2"/>
       <c t="s" r="AA141" s="2">
-        <v>363</v>
+        <v>469</v>
       </c>
     </row>
     <row r="142" ht="12.75" customHeight="1">
@@ -23447,7 +23441,7 @@
       <c r="B142" s="8"/>
       <c r="C142" s="8"/>
       <c t="s" r="E142" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
@@ -23484,10 +23478,10 @@
       <c r="C143" s="8"/>
       <c r="D143" s="8"/>
       <c t="s" r="F143" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c t="s" r="G143" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H143" s="3"/>
       <c r="I143" s="9"/>
@@ -23496,10 +23490,10 @@
       </c>
       <c r="K143" s="3"/>
       <c t="s" r="L143" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c t="s" r="M143" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N143" s="5"/>
       <c r="O143" s="3"/>
@@ -23536,22 +23530,22 @@
       <c r="C144" s="8"/>
       <c r="D144" s="8"/>
       <c t="s" r="F144" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c t="s" r="G144" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="H144" s="3"/>
       <c r="I144" s="9"/>
       <c t="s" r="J144" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K144" s="3"/>
       <c t="s" r="L144" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c t="s" r="M144" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N144" s="5"/>
       <c r="O144" s="3"/>
@@ -23581,7 +23575,7 @@
       <c r="Y144" s="2"/>
       <c r="Z144" s="2"/>
       <c t="s" r="AA144" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -23590,10 +23584,10 @@
       <c r="C145" s="8"/>
       <c r="D145" s="8"/>
       <c t="s" r="F145" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c t="s" r="G145" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="H145" s="3"/>
       <c r="I145" s="9"/>
@@ -23602,10 +23596,10 @@
       </c>
       <c r="K145" s="3"/>
       <c t="s" r="L145" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c t="s" r="M145" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N145" s="5"/>
       <c r="O145" s="3"/>
@@ -23642,22 +23636,22 @@
       <c r="C146" s="8"/>
       <c r="D146" s="8"/>
       <c t="s" r="F146" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c t="s" r="G146" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="H146" s="3"/>
       <c r="I146" s="9"/>
       <c t="s" r="J146" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K146" s="3"/>
       <c t="s" r="L146" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c t="s" r="M146" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="N146" s="5"/>
       <c r="O146" s="3"/>
@@ -23687,7 +23681,7 @@
       <c r="Y146" s="2"/>
       <c r="Z146" s="2"/>
       <c t="s" r="AA146" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="147" ht="15" customHeight="1">
@@ -23696,10 +23690,10 @@
       <c r="C147" s="8"/>
       <c r="D147" s="8"/>
       <c t="s" r="F147" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c t="s" r="G147" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="H147" s="3"/>
       <c r="I147" s="9"/>
@@ -23708,7 +23702,7 @@
       </c>
       <c r="K147" s="3"/>
       <c t="s" r="L147" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c t="s" r="M147" s="2">
         <v>220</v>
@@ -23748,13 +23742,13 @@
       <c r="C148" s="8"/>
       <c r="D148" s="8"/>
       <c t="s" r="F148" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c t="s" r="G148" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c t="s" r="H148" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="I148" s="9"/>
       <c t="s" r="J148" s="2">
@@ -23762,7 +23756,7 @@
       </c>
       <c r="K148" s="3"/>
       <c t="s" r="L148" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c t="s" r="M148" s="2">
         <v>220</v>
@@ -23802,13 +23796,13 @@
       <c r="C149" s="8"/>
       <c r="D149" s="8"/>
       <c t="s" r="F149" s="2">
+        <v>495</v>
+      </c>
+      <c t="s" r="G149" s="2">
         <v>493</v>
       </c>
-      <c t="s" r="G149" s="2">
-        <v>491</v>
-      </c>
       <c t="s" r="H149" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="I149" s="9"/>
       <c t="s" r="J149" s="2">
@@ -23816,10 +23810,10 @@
       </c>
       <c r="K149" s="3"/>
       <c t="s" r="L149" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c t="s" r="M149" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N149" s="5"/>
       <c r="O149" s="3"/>
@@ -23856,10 +23850,10 @@
       <c r="C150" s="8"/>
       <c r="D150" s="8"/>
       <c t="s" r="F150" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c t="s" r="G150" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="H150" s="3"/>
       <c r="I150" s="9"/>
@@ -23868,10 +23862,10 @@
       </c>
       <c r="K150" s="3"/>
       <c t="s" r="L150" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c t="s" r="M150" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N150" s="5"/>
       <c r="O150" s="3"/>
@@ -23901,7 +23895,7 @@
       <c r="Y150" s="2"/>
       <c r="Z150" s="2"/>
       <c t="s" r="AA150" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="151" ht="12.75" customHeight="1">
@@ -23909,7 +23903,7 @@
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
       <c t="s" r="E151" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
@@ -23946,10 +23940,10 @@
       <c r="C152" s="8"/>
       <c r="D152" s="8"/>
       <c t="s" r="F152" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c t="s" r="G152" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="H152" s="3"/>
       <c r="I152" s="9"/>
@@ -23958,7 +23952,7 @@
       </c>
       <c r="K152" s="3"/>
       <c t="s" r="L152" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c t="s" r="M152" s="2">
         <v>85</v>
@@ -23991,7 +23985,7 @@
       <c r="Y152" s="2"/>
       <c r="Z152" s="2"/>
       <c t="s" r="AA152" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="153" ht="12.75" customHeight="1">
@@ -23999,7 +23993,7 @@
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
       <c t="s" r="E153" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
@@ -24036,10 +24030,10 @@
       <c r="C154" s="8"/>
       <c r="D154" s="8"/>
       <c t="s" r="F154" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c t="s" r="G154" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H154" s="3"/>
       <c r="I154" s="9"/>
@@ -24048,7 +24042,7 @@
       </c>
       <c r="K154" s="3"/>
       <c t="s" r="L154" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c t="s" r="M154" s="2">
         <v>167</v>
@@ -24088,10 +24082,10 @@
       <c r="C155" s="8"/>
       <c r="D155" s="8"/>
       <c t="s" r="F155" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c t="s" r="G155" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="H155" s="3"/>
       <c r="I155" s="9"/>
@@ -24100,7 +24094,7 @@
       </c>
       <c r="K155" s="3"/>
       <c t="s" r="L155" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c t="s" r="M155" s="2">
         <v>294</v>
@@ -24133,7 +24127,7 @@
       <c r="Y155" s="2"/>
       <c r="Z155" s="2"/>
       <c t="s" r="AA155" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="156" ht="12.75" customHeight="1">
@@ -24141,7 +24135,7 @@
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
       <c t="s" r="E156" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
@@ -24178,10 +24172,10 @@
       <c r="C157" s="8"/>
       <c r="D157" s="8"/>
       <c t="s" r="F157" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c t="s" r="G157" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="H157" s="3"/>
       <c r="I157" s="9"/>
@@ -24190,7 +24184,7 @@
       </c>
       <c r="K157" s="3"/>
       <c t="s" r="L157" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c t="s" r="M157" s="2">
         <v>246</v>
@@ -24229,7 +24223,7 @@
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
       <c t="s" r="E158" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
@@ -24266,10 +24260,10 @@
       <c r="C159" s="8"/>
       <c r="D159" s="8"/>
       <c t="s" r="F159" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c t="s" r="G159" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="H159" s="3"/>
       <c r="I159" s="9"/>
@@ -24278,7 +24272,7 @@
       </c>
       <c r="K159" s="3"/>
       <c t="s" r="L159" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c t="s" r="M159" s="2">
         <v>275</v>
@@ -24311,7 +24305,7 @@
       <c r="Y159" s="2"/>
       <c r="Z159" s="2"/>
       <c t="s" r="AA159" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="160" ht="12.75" customHeight="1">
@@ -24319,7 +24313,7 @@
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
       <c t="s" r="E160" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
@@ -24356,19 +24350,19 @@
       <c r="C161" s="8"/>
       <c r="D161" s="8"/>
       <c t="s" r="F161" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c t="s" r="G161" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="H161" s="3"/>
       <c r="I161" s="9"/>
       <c t="s" r="J161" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K161" s="3"/>
       <c t="s" r="L161" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c t="s" r="M161" s="2">
         <v>85</v>
@@ -24401,7 +24395,7 @@
       <c r="Y161" s="2"/>
       <c r="Z161" s="2"/>
       <c t="s" r="AA161" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="162" ht="12.75" customHeight="1">
@@ -24409,7 +24403,7 @@
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
       <c t="s" r="E162" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
@@ -24446,22 +24440,22 @@
       <c r="C163" s="8"/>
       <c r="D163" s="8"/>
       <c t="s" r="F163" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c t="s" r="G163" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="H163" s="3"/>
       <c r="I163" s="9"/>
       <c t="s" r="J163" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K163" s="3"/>
       <c t="s" r="L163" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c t="s" r="M163" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N163" s="5"/>
       <c r="O163" s="3"/>
@@ -24498,22 +24492,22 @@
       <c r="C164" s="8"/>
       <c r="D164" s="8"/>
       <c t="s" r="F164" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c t="s" r="G164" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="H164" s="3"/>
       <c r="I164" s="9"/>
       <c t="s" r="J164" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="K164" s="3"/>
       <c t="s" r="L164" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c t="s" r="M164" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="N164" s="5"/>
       <c r="O164" s="3"/>
@@ -24550,10 +24544,10 @@
       <c r="C165" s="8"/>
       <c r="D165" s="8"/>
       <c t="s" r="F165" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c t="s" r="G165" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="H165" s="3"/>
       <c r="I165" s="9"/>
@@ -24562,10 +24556,10 @@
       </c>
       <c r="K165" s="3"/>
       <c t="s" r="L165" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c t="s" r="M165" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N165" s="5"/>
       <c r="O165" s="3"/>
@@ -24602,19 +24596,19 @@
       <c r="C166" s="8"/>
       <c r="D166" s="8"/>
       <c t="s" r="F166" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c t="s" r="G166" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="H166" s="3"/>
       <c r="I166" s="9"/>
       <c t="s" r="J166" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K166" s="3"/>
       <c t="s" r="L166" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c t="s" r="M166" s="2">
         <v>85</v>
@@ -24647,7 +24641,7 @@
       <c r="Y166" s="2"/>
       <c r="Z166" s="2"/>
       <c t="s" r="AA166" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="167" ht="15" customHeight="1">
@@ -24656,13 +24650,13 @@
       <c r="C167" s="8"/>
       <c r="D167" s="8"/>
       <c t="s" r="F167" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c t="s" r="G167" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c t="s" r="H167" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="I167" s="9"/>
       <c t="s" r="J167" s="2">
@@ -24670,10 +24664,10 @@
       </c>
       <c r="K167" s="3"/>
       <c t="s" r="L167" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c t="s" r="M167" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="N167" s="5"/>
       <c r="O167" s="3"/>
@@ -24710,24 +24704,24 @@
       <c r="C168" s="8"/>
       <c r="D168" s="8"/>
       <c t="s" r="F168" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c t="s" r="G168" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c t="s" r="H168" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="I168" s="9"/>
       <c t="s" r="J168" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K168" s="3"/>
       <c t="s" r="L168" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c t="s" r="M168" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N168" s="5"/>
       <c r="O168" s="3"/>
@@ -24764,24 +24758,24 @@
       <c r="C169" s="8"/>
       <c r="D169" s="8"/>
       <c t="s" r="F169" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c t="s" r="G169" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c t="s" r="H169" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="I169" s="9"/>
       <c t="s" r="J169" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K169" s="3"/>
       <c t="s" r="L169" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c t="s" r="M169" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="N169" s="5"/>
       <c r="O169" s="3"/>
@@ -24818,10 +24812,10 @@
       <c r="C170" s="8"/>
       <c r="D170" s="8"/>
       <c t="s" r="F170" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c t="s" r="G170" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="H170" s="3"/>
       <c r="I170" s="9"/>
@@ -24830,7 +24824,7 @@
       </c>
       <c r="K170" s="3"/>
       <c t="s" r="L170" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c t="s" r="M170" s="2">
         <v>85</v>
@@ -24863,7 +24857,7 @@
       <c r="Y170" s="2"/>
       <c r="Z170" s="2"/>
       <c t="s" r="AA170" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="171" ht="15" customHeight="1">
@@ -24872,10 +24866,10 @@
       <c r="C171" s="8"/>
       <c r="D171" s="8"/>
       <c t="s" r="F171" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c t="s" r="G171" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="H171" s="3"/>
       <c r="I171" s="9"/>
@@ -24884,10 +24878,10 @@
       </c>
       <c r="K171" s="3"/>
       <c t="s" r="L171" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c t="s" r="M171" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N171" s="5"/>
       <c r="O171" s="3"/>
@@ -24917,7 +24911,7 @@
       <c r="Y171" s="2"/>
       <c r="Z171" s="2"/>
       <c t="s" r="AA171" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="172" ht="12.75" customHeight="1">
@@ -24925,7 +24919,7 @@
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
       <c t="s" r="E172" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
@@ -24962,13 +24956,13 @@
       <c r="C173" s="8"/>
       <c r="D173" s="8"/>
       <c t="s" r="F173" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c t="s" r="G173" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c t="s" r="H173" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="I173" s="9"/>
       <c t="s" r="J173" s="2">
@@ -24976,10 +24970,10 @@
       </c>
       <c r="K173" s="3"/>
       <c t="s" r="L173" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c t="s" r="M173" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N173" s="5"/>
       <c r="O173" s="3"/>
@@ -25016,13 +25010,13 @@
       <c r="C174" s="8"/>
       <c r="D174" s="8"/>
       <c t="s" r="F174" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c t="s" r="G174" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c t="s" r="H174" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="I174" s="9"/>
       <c t="s" r="J174" s="2">
@@ -25030,10 +25024,10 @@
       </c>
       <c r="K174" s="3"/>
       <c t="s" r="L174" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c t="s" r="M174" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="N174" s="5"/>
       <c r="O174" s="3"/>
@@ -25069,7 +25063,7 @@
       <c r="B175" s="8"/>
       <c r="C175" s="8"/>
       <c t="s" r="E175" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
@@ -25106,13 +25100,13 @@
       <c r="C176" s="8"/>
       <c r="D176" s="8"/>
       <c t="s" r="F176" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c t="s" r="G176" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c t="s" r="H176" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="I176" s="9"/>
       <c t="s" r="J176" s="2">
@@ -25120,10 +25114,10 @@
       </c>
       <c r="K176" s="3"/>
       <c t="s" r="L176" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c t="s" r="M176" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="N176" s="5"/>
       <c r="O176" s="3"/>
@@ -25160,24 +25154,24 @@
       <c r="C177" s="8"/>
       <c r="D177" s="8"/>
       <c t="s" r="F177" s="2">
+        <v>576</v>
+      </c>
+      <c t="s" r="G177" s="2">
         <v>574</v>
       </c>
-      <c t="s" r="G177" s="2">
-        <v>572</v>
-      </c>
       <c t="s" r="H177" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="I177" s="9"/>
       <c t="s" r="J177" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="K177" s="3"/>
       <c t="s" r="L177" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c t="s" r="M177" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N177" s="5"/>
       <c r="O177" s="3"/>
@@ -25213,7 +25207,7 @@
       <c r="B178" s="8"/>
       <c r="C178" s="8"/>
       <c t="s" r="E178" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
@@ -25250,24 +25244,24 @@
       <c r="C179" s="8"/>
       <c r="D179" s="8"/>
       <c t="s" r="F179" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c t="s" r="G179" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c t="s" r="H179" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="I179" s="9"/>
       <c t="s" r="J179" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K179" s="3"/>
       <c t="s" r="L179" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c t="s" r="M179" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="N179" s="5"/>
       <c r="O179" s="3"/>
@@ -25304,24 +25298,24 @@
       <c r="C180" s="8"/>
       <c r="D180" s="8"/>
       <c t="s" r="F180" s="2">
+        <v>584</v>
+      </c>
+      <c t="s" r="G180" s="2">
         <v>582</v>
       </c>
-      <c t="s" r="G180" s="2">
-        <v>580</v>
-      </c>
       <c t="s" r="H180" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="I180" s="9"/>
       <c t="s" r="J180" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K180" s="3"/>
       <c t="s" r="L180" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c t="s" r="M180" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N180" s="5"/>
       <c r="O180" s="3"/>
@@ -25357,7 +25351,7 @@
       <c r="B181" s="8"/>
       <c r="C181" s="8"/>
       <c t="s" r="E181" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
@@ -25394,13 +25388,13 @@
       <c r="C182" s="8"/>
       <c r="D182" s="8"/>
       <c t="s" r="F182" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c t="s" r="G182" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c t="s" r="H182" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="I182" s="9"/>
       <c t="s" r="J182" s="2">
@@ -25408,10 +25402,10 @@
       </c>
       <c r="K182" s="3"/>
       <c t="s" r="L182" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c t="s" r="M182" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N182" s="5"/>
       <c r="O182" s="3"/>
@@ -25448,13 +25442,13 @@
       <c r="C183" s="8"/>
       <c r="D183" s="8"/>
       <c t="s" r="F183" s="2">
+        <v>591</v>
+      </c>
+      <c t="s" r="G183" s="2">
         <v>589</v>
       </c>
-      <c t="s" r="G183" s="2">
-        <v>587</v>
-      </c>
       <c t="s" r="H183" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="I183" s="9"/>
       <c t="s" r="J183" s="2">
@@ -25462,10 +25456,10 @@
       </c>
       <c r="K183" s="3"/>
       <c t="s" r="L183" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c t="s" r="M183" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N183" s="5"/>
       <c r="O183" s="3"/>
@@ -25501,7 +25495,7 @@
       <c r="B184" s="8"/>
       <c r="C184" s="8"/>
       <c t="s" r="E184" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
@@ -25538,19 +25532,19 @@
       <c r="C185" s="8"/>
       <c r="D185" s="8"/>
       <c t="s" r="F185" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c t="s" r="G185" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="H185" s="3"/>
       <c r="I185" s="9"/>
       <c t="s" r="J185" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K185" s="3"/>
       <c t="s" r="L185" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c t="s" r="M185" s="2">
         <v>214</v>
@@ -25583,7 +25577,7 @@
       <c r="Y185" s="2"/>
       <c r="Z185" s="2"/>
       <c t="s" r="AA185" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="186" ht="15" customHeight="1">
@@ -25592,19 +25586,19 @@
       <c r="C186" s="8"/>
       <c r="D186" s="8"/>
       <c t="s" r="F186" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c t="s" r="G186" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H186" s="3"/>
       <c r="I186" s="9"/>
       <c t="s" r="J186" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="K186" s="3"/>
       <c t="s" r="L186" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c t="s" r="M186" s="2">
         <v>220</v>
@@ -25643,7 +25637,7 @@
       <c r="B187" s="8"/>
       <c r="C187" s="8"/>
       <c t="s" r="E187" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
@@ -25680,22 +25674,22 @@
       <c r="C188" s="8"/>
       <c r="D188" s="8"/>
       <c t="s" r="F188" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c t="s" r="G188" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="H188" s="3"/>
       <c r="I188" s="9"/>
       <c t="s" r="J188" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="K188" s="3"/>
       <c t="s" r="L188" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c t="s" r="M188" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="N188" s="5"/>
       <c r="O188" s="3"/>
@@ -25731,7 +25725,7 @@
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
       <c t="s" r="E189" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
@@ -25768,10 +25762,10 @@
       <c r="C190" s="8"/>
       <c r="D190" s="8"/>
       <c t="s" r="F190" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c t="s" r="G190" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="H190" s="3"/>
       <c r="I190" s="9"/>
@@ -25780,7 +25774,7 @@
       </c>
       <c r="K190" s="3"/>
       <c t="s" r="L190" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c t="s" r="M190" s="2">
         <v>294</v>
@@ -25813,7 +25807,7 @@
       <c r="Y190" s="2"/>
       <c r="Z190" s="2"/>
       <c t="s" r="AA190" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="191" ht="15" customHeight="1">
@@ -25822,13 +25816,13 @@
       <c r="C191" s="8"/>
       <c r="D191" s="8"/>
       <c t="s" r="F191" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c t="s" r="G191" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c t="s" r="H191" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="I191" s="9"/>
       <c t="s" r="J191" s="2">
@@ -25836,10 +25830,10 @@
       </c>
       <c r="K191" s="3"/>
       <c t="s" r="L191" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c t="s" r="M191" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="N191" s="5"/>
       <c r="O191" s="3"/>
@@ -25876,13 +25870,13 @@
       <c r="C192" s="8"/>
       <c r="D192" s="8"/>
       <c t="s" r="F192" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c t="s" r="G192" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c t="s" r="H192" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="I192" s="9"/>
       <c t="s" r="J192" s="2">
@@ -25890,10 +25884,10 @@
       </c>
       <c r="K192" s="3"/>
       <c t="s" r="L192" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c t="s" r="M192" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="N192" s="5"/>
       <c r="O192" s="3"/>
@@ -25930,10 +25924,10 @@
       <c r="C193" s="8"/>
       <c r="D193" s="8"/>
       <c t="s" r="F193" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c t="s" r="G193" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="H193" s="3"/>
       <c r="I193" s="9"/>
@@ -25942,10 +25936,10 @@
       </c>
       <c r="K193" s="3"/>
       <c t="s" r="L193" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c t="s" r="M193" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="N193" s="5"/>
       <c r="O193" s="3"/>
@@ -25975,7 +25969,7 @@
       <c r="Y193" s="2"/>
       <c r="Z193" s="2"/>
       <c t="s" r="AA193" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="194" ht="15" customHeight="1">
@@ -25984,19 +25978,19 @@
       <c r="C194" s="8"/>
       <c r="D194" s="8"/>
       <c t="s" r="F194" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c t="s" r="G194" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="H194" s="3"/>
       <c r="I194" s="9"/>
       <c t="s" r="J194" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K194" s="3"/>
       <c t="s" r="L194" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c t="s" r="M194" s="2">
         <v>85</v>
@@ -26029,7 +26023,7 @@
       <c r="Y194" s="2"/>
       <c r="Z194" s="2"/>
       <c t="s" r="AA194" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="195" ht="12.75" customHeight="1">
@@ -26037,7 +26031,7 @@
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
       <c t="s" r="E195" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
@@ -26074,22 +26068,22 @@
       <c r="C196" s="8"/>
       <c r="D196" s="8"/>
       <c t="s" r="F196" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c t="s" r="G196" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="H196" s="3"/>
       <c r="I196" s="9"/>
       <c t="s" r="J196" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="K196" s="3"/>
       <c t="s" r="L196" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c t="s" r="M196" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N196" s="5"/>
       <c r="O196" s="3"/>
@@ -26125,7 +26119,7 @@
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
       <c t="s" r="E197" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
@@ -26162,24 +26156,24 @@
       <c r="C198" s="8"/>
       <c r="D198" s="8"/>
       <c t="s" r="F198" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c t="s" r="G198" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c t="s" r="H198" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="I198" s="9"/>
       <c t="s" r="J198" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K198" s="3"/>
       <c t="s" r="L198" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c t="s" r="M198" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="N198" s="5"/>
       <c r="O198" s="3"/>
@@ -26216,13 +26210,13 @@
       <c r="C199" s="8"/>
       <c r="D199" s="8"/>
       <c t="s" r="F199" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c t="s" r="G199" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c t="s" r="H199" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="I199" s="9"/>
       <c t="s" r="J199" s="2">
@@ -26230,10 +26224,10 @@
       </c>
       <c r="K199" s="3"/>
       <c t="s" r="L199" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c t="s" r="M199" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N199" s="5"/>
       <c r="O199" s="3"/>
@@ -26269,7 +26263,7 @@
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
       <c t="s" r="E200" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
@@ -26306,19 +26300,19 @@
       <c r="C201" s="8"/>
       <c r="D201" s="8"/>
       <c t="s" r="F201" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c t="s" r="G201" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="H201" s="3"/>
       <c r="I201" s="9"/>
       <c t="s" r="J201" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="K201" s="3"/>
       <c t="s" r="L201" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c t="s" r="M201" s="2">
         <v>305</v>
@@ -26357,7 +26351,7 @@
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
       <c t="s" r="E202" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
@@ -26394,22 +26388,22 @@
       <c r="C203" s="8"/>
       <c r="D203" s="8"/>
       <c t="s" r="F203" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c t="s" r="G203" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="H203" s="3"/>
       <c r="I203" s="9"/>
       <c t="s" r="J203" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="K203" s="3"/>
       <c t="s" r="L203" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c t="s" r="M203" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="N203" s="5"/>
       <c r="O203" s="3"/>
@@ -26446,10 +26440,10 @@
       <c r="C204" s="8"/>
       <c r="D204" s="8"/>
       <c t="s" r="F204" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c t="s" r="G204" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="H204" s="3"/>
       <c r="I204" s="9"/>
@@ -26458,10 +26452,10 @@
       </c>
       <c r="K204" s="3"/>
       <c t="s" r="L204" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c t="s" r="M204" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="N204" s="5"/>
       <c r="O204" s="3"/>
@@ -26497,7 +26491,7 @@
       <c r="B205" s="8"/>
       <c r="C205" s="8"/>
       <c t="s" r="E205" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
@@ -26534,22 +26528,22 @@
       <c r="C206" s="8"/>
       <c r="D206" s="8"/>
       <c t="s" r="F206" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c t="s" r="G206" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="H206" s="3"/>
       <c r="I206" s="9"/>
       <c t="s" r="J206" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="K206" s="3"/>
       <c t="s" r="L206" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c t="s" r="M206" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N206" s="5"/>
       <c r="O206" s="3"/>
@@ -26579,7 +26573,7 @@
       <c r="Y206" s="2"/>
       <c r="Z206" s="2"/>
       <c t="s" r="AA206" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="207" ht="15" customHeight="1">
@@ -26588,24 +26582,24 @@
       <c r="C207" s="8"/>
       <c r="D207" s="8"/>
       <c t="s" r="F207" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c t="s" r="G207" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c t="s" r="H207" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="I207" s="9"/>
       <c t="s" r="J207" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K207" s="3"/>
       <c t="s" r="L207" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c t="s" r="M207" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="N207" s="5"/>
       <c r="O207" s="3"/>
@@ -26642,13 +26636,13 @@
       <c r="C208" s="8"/>
       <c r="D208" s="8"/>
       <c t="s" r="F208" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c t="s" r="G208" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c t="s" r="H208" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="I208" s="9"/>
       <c t="s" r="J208" s="2">
@@ -26656,7 +26650,7 @@
       </c>
       <c r="K208" s="3"/>
       <c t="s" r="L208" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c t="s" r="M208" s="2">
         <v>120</v>
@@ -26696,24 +26690,24 @@
       <c r="C209" s="8"/>
       <c r="D209" s="8"/>
       <c t="s" r="F209" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c t="s" r="G209" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c t="s" r="H209" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="I209" s="9"/>
       <c t="s" r="J209" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="K209" s="3"/>
       <c t="s" r="L209" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c t="s" r="M209" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="N209" s="5"/>
       <c r="O209" s="3"/>
@@ -26743,7 +26737,7 @@
       <c r="Y209" s="2"/>
       <c r="Z209" s="2"/>
       <c t="s" r="AA209" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -26752,13 +26746,13 @@
       <c r="C210" s="8"/>
       <c r="D210" s="8"/>
       <c t="s" r="F210" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c t="s" r="G210" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c t="s" r="H210" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="I210" s="9"/>
       <c t="s" r="J210" s="2">
@@ -26766,7 +26760,7 @@
       </c>
       <c r="K210" s="3"/>
       <c t="s" r="L210" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c t="s" r="M210" s="2">
         <v>85</v>
@@ -26799,7 +26793,7 @@
       <c r="Y210" s="2"/>
       <c r="Z210" s="2"/>
       <c t="s" r="AA210" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="211" ht="12.75" customHeight="1">
@@ -26807,7 +26801,7 @@
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
       <c t="s" r="E211" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
@@ -26844,22 +26838,22 @@
       <c r="C212" s="8"/>
       <c r="D212" s="8"/>
       <c t="s" r="F212" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c t="s" r="G212" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="H212" s="3"/>
       <c r="I212" s="9"/>
       <c t="s" r="J212" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="K212" s="3"/>
       <c t="s" r="L212" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c t="s" r="M212" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="N212" s="5"/>
       <c r="O212" s="3"/>
@@ -26894,7 +26888,7 @@
       <c r="A213" s="8"/>
       <c r="B213" s="8"/>
       <c t="s" r="D213" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
@@ -26931,7 +26925,7 @@
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
       <c t="s" r="E214" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
@@ -26968,10 +26962,10 @@
       <c r="C215" s="8"/>
       <c r="D215" s="8"/>
       <c t="s" r="F215" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c t="s" r="G215" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="H215" s="3"/>
       <c r="I215" s="9"/>
@@ -26980,7 +26974,7 @@
       </c>
       <c r="K215" s="3"/>
       <c t="s" r="L215" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c t="s" r="M215" s="2">
         <v>85</v>
@@ -27013,7 +27007,7 @@
       <c r="Y215" s="2"/>
       <c r="Z215" s="2"/>
       <c t="s" r="AA215" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="216" ht="12.75" customHeight="1">
@@ -27021,7 +27015,7 @@
       <c r="B216" s="8"/>
       <c r="C216" s="8"/>
       <c t="s" r="E216" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
@@ -27058,22 +27052,22 @@
       <c r="C217" s="8"/>
       <c r="D217" s="8"/>
       <c t="s" r="F217" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c t="s" r="G217" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="H217" s="3"/>
       <c r="I217" s="9"/>
       <c t="s" r="J217" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K217" s="3"/>
       <c t="s" r="L217" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c t="s" r="M217" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N217" s="5"/>
       <c r="O217" s="3"/>
@@ -27108,7 +27102,7 @@
       <c r="A218" s="8"/>
       <c r="B218" s="8"/>
       <c t="s" r="D218" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E218" s="2"/>
       <c r="F218" s="2"/>
@@ -27145,11 +27139,11 @@
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
       <c t="s" r="E219" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="F219" s="2"/>
       <c t="s" r="G219" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="H219" s="3"/>
       <c r="I219" s="9"/>
@@ -27158,7 +27152,7 @@
       </c>
       <c r="K219" s="3"/>
       <c t="s" r="L219" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c t="s" r="M219" s="2">
         <v>292</v>
@@ -27197,11 +27191,11 @@
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
       <c t="s" r="E220" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F220" s="2"/>
       <c t="s" r="G220" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="H220" s="3"/>
       <c r="I220" s="9"/>
@@ -27210,7 +27204,7 @@
       </c>
       <c r="K220" s="3"/>
       <c t="s" r="L220" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c t="s" r="M220" s="2">
         <v>292</v>
@@ -27249,11 +27243,11 @@
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
       <c t="s" r="E221" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="F221" s="2"/>
       <c t="s" r="G221" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="H221" s="3"/>
       <c r="I221" s="9"/>
@@ -27262,7 +27256,7 @@
       </c>
       <c r="K221" s="3"/>
       <c t="s" r="L221" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c t="s" r="M221" s="2">
         <v>292</v>
@@ -27301,11 +27295,11 @@
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
       <c t="s" r="E222" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="F222" s="2"/>
       <c t="s" r="G222" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="H222" s="3"/>
       <c r="I222" s="9"/>
@@ -27314,10 +27308,10 @@
       </c>
       <c r="K222" s="3"/>
       <c t="s" r="L222" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c t="s" r="M222" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="N222" s="5"/>
       <c r="O222" s="3"/>
@@ -27353,11 +27347,11 @@
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
       <c t="s" r="E223" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F223" s="2"/>
       <c t="s" r="G223" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H223" s="3"/>
       <c r="I223" s="9"/>
@@ -27366,10 +27360,10 @@
       </c>
       <c r="K223" s="3"/>
       <c t="s" r="L223" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c t="s" r="M223" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N223" s="5"/>
       <c r="O223" s="3"/>
@@ -27404,7 +27398,7 @@
       <c r="A224" s="8"/>
       <c r="B224" s="8"/>
       <c t="s" r="D224" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
@@ -27441,20 +27435,20 @@
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
       <c t="s" r="E225" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="F225" s="2"/>
       <c t="s" r="G225" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="H225" s="3"/>
       <c r="I225" s="9"/>
       <c t="s" r="J225" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="K225" s="3"/>
       <c t="s" r="L225" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c t="s" r="M225" s="2">
         <v>167</v>
@@ -27493,23 +27487,23 @@
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
       <c t="s" r="E226" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="F226" s="2"/>
       <c t="s" r="G226" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="H226" s="3"/>
       <c r="I226" s="9"/>
       <c t="s" r="J226" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="K226" s="3"/>
       <c t="s" r="L226" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c t="s" r="M226" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="N226" s="5"/>
       <c r="O226" s="3"/>
@@ -27545,20 +27539,20 @@
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
       <c t="s" r="E227" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F227" s="2"/>
       <c t="s" r="G227" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="H227" s="3"/>
       <c r="I227" s="9"/>
       <c t="s" r="J227" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K227" s="3"/>
       <c t="s" r="L227" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c t="s" r="M227" s="2">
         <v>41</v>
@@ -27597,11 +27591,11 @@
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
       <c t="s" r="E228" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="F228" s="2"/>
       <c t="s" r="G228" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="H228" s="3"/>
       <c r="I228" s="9"/>
@@ -27610,10 +27604,10 @@
       </c>
       <c r="K228" s="3"/>
       <c t="s" r="L228" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c t="s" r="M228" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="N228" s="5"/>
       <c r="O228" s="3"/>
@@ -27649,11 +27643,11 @@
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
       <c t="s" r="E229" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="F229" s="2"/>
       <c t="s" r="G229" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="H229" s="3"/>
       <c r="I229" s="9"/>
@@ -27662,7 +27656,7 @@
       </c>
       <c r="K229" s="3"/>
       <c t="s" r="L229" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c t="s" r="M229" s="2">
         <v>305</v>
@@ -27701,11 +27695,11 @@
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
       <c t="s" r="E230" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F230" s="2"/>
       <c t="s" r="G230" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="H230" s="3"/>
       <c r="I230" s="9"/>
@@ -27714,10 +27708,10 @@
       </c>
       <c r="K230" s="3"/>
       <c t="s" r="L230" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c t="s" r="M230" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="N230" s="5"/>
       <c r="O230" s="3"/>
@@ -27753,23 +27747,23 @@
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
       <c t="s" r="E231" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="F231" s="2"/>
       <c t="s" r="G231" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="H231" s="3"/>
       <c r="I231" s="9"/>
       <c t="s" r="J231" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K231" s="3"/>
       <c t="s" r="L231" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c t="s" r="M231" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N231" s="5"/>
       <c r="O231" s="3"/>
@@ -27805,11 +27799,11 @@
       <c r="B232" s="8"/>
       <c r="C232" s="8"/>
       <c t="s" r="E232" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="F232" s="2"/>
       <c t="s" r="G232" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="H232" s="3"/>
       <c r="I232" s="9"/>
@@ -27818,7 +27812,7 @@
       </c>
       <c r="K232" s="3"/>
       <c t="s" r="L232" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c t="s" r="M232" s="2">
         <v>305</v>
@@ -27857,11 +27851,11 @@
       <c r="B233" s="8"/>
       <c r="C233" s="8"/>
       <c t="s" r="E233" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="F233" s="2"/>
       <c t="s" r="G233" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="H233" s="3"/>
       <c r="I233" s="9"/>
@@ -27870,10 +27864,10 @@
       </c>
       <c r="K233" s="3"/>
       <c t="s" r="L233" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c t="s" r="M233" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="N233" s="5"/>
       <c r="O233" s="3"/>
@@ -27909,11 +27903,11 @@
       <c r="B234" s="8"/>
       <c r="C234" s="8"/>
       <c t="s" r="E234" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="F234" s="2"/>
       <c t="s" r="G234" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="H234" s="3"/>
       <c r="I234" s="9"/>
@@ -27922,10 +27916,10 @@
       </c>
       <c r="K234" s="3"/>
       <c t="s" r="L234" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c t="s" r="M234" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="N234" s="5"/>
       <c r="O234" s="3"/>
@@ -27961,23 +27955,23 @@
       <c r="B235" s="8"/>
       <c r="C235" s="8"/>
       <c t="s" r="E235" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="F235" s="2"/>
       <c t="s" r="G235" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="H235" s="3"/>
       <c r="I235" s="9"/>
       <c t="s" r="J235" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="K235" s="3"/>
       <c t="s" r="L235" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c t="s" r="M235" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N235" s="5"/>
       <c r="O235" s="3"/>
@@ -28013,11 +28007,11 @@
       <c r="B236" s="8"/>
       <c r="C236" s="8"/>
       <c t="s" r="E236" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="F236" s="2"/>
       <c t="s" r="G236" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="H236" s="3"/>
       <c r="I236" s="9"/>
@@ -28026,10 +28020,10 @@
       </c>
       <c r="K236" s="3"/>
       <c t="s" r="L236" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c t="s" r="M236" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N236" s="5"/>
       <c r="O236" s="3"/>
@@ -28065,23 +28059,23 @@
       <c r="B237" s="8"/>
       <c r="C237" s="8"/>
       <c t="s" r="E237" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="F237" s="2"/>
       <c t="s" r="G237" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="H237" s="3"/>
       <c r="I237" s="9"/>
       <c t="s" r="J237" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K237" s="3"/>
       <c t="s" r="L237" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c t="s" r="M237" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="N237" s="5"/>
       <c r="O237" s="3"/>
@@ -28117,11 +28111,11 @@
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
       <c t="s" r="E238" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F238" s="2"/>
       <c t="s" r="G238" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="H238" s="3"/>
       <c r="I238" s="9"/>
@@ -28130,7 +28124,7 @@
       </c>
       <c r="K238" s="3"/>
       <c t="s" r="L238" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c t="s" r="M238" s="2">
         <v>141</v>
@@ -28169,11 +28163,11 @@
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
       <c t="s" r="E239" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="F239" s="2"/>
       <c t="s" r="G239" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="H239" s="3"/>
       <c r="I239" s="9"/>
@@ -28182,10 +28176,10 @@
       </c>
       <c r="K239" s="3"/>
       <c t="s" r="L239" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c t="s" r="M239" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="N239" s="5"/>
       <c r="O239" s="3"/>
@@ -28221,11 +28215,11 @@
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
       <c t="s" r="E240" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="F240" s="2"/>
       <c t="s" r="G240" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="H240" s="3"/>
       <c r="I240" s="9"/>
@@ -28234,10 +28228,10 @@
       </c>
       <c r="K240" s="3"/>
       <c t="s" r="L240" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c t="s" r="M240" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="N240" s="5"/>
       <c r="O240" s="3"/>
@@ -28273,23 +28267,23 @@
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
       <c t="s" r="E241" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="F241" s="2"/>
       <c t="s" r="G241" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="H241" s="3"/>
       <c r="I241" s="9"/>
       <c t="s" r="J241" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K241" s="3"/>
       <c t="s" r="L241" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c t="s" r="M241" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="N241" s="5"/>
       <c r="O241" s="3"/>
@@ -28325,11 +28319,11 @@
       <c r="B242" s="8"/>
       <c r="C242" s="8"/>
       <c t="s" r="E242" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="F242" s="2"/>
       <c t="s" r="G242" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="H242" s="3"/>
       <c r="I242" s="9"/>
@@ -28338,10 +28332,10 @@
       </c>
       <c r="K242" s="3"/>
       <c t="s" r="L242" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c t="s" r="M242" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="N242" s="5"/>
       <c r="O242" s="3"/>
@@ -28377,23 +28371,23 @@
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
       <c t="s" r="E243" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="F243" s="2"/>
       <c t="s" r="G243" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H243" s="3"/>
       <c r="I243" s="9"/>
       <c t="s" r="J243" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="K243" s="3"/>
       <c t="s" r="L243" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c t="s" r="M243" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="N243" s="5"/>
       <c r="O243" s="3"/>
@@ -28429,23 +28423,23 @@
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
       <c t="s" r="E244" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="F244" s="2"/>
       <c t="s" r="G244" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="H244" s="3"/>
       <c r="I244" s="9"/>
       <c t="s" r="J244" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K244" s="3"/>
       <c t="s" r="L244" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c t="s" r="M244" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N244" s="5"/>
       <c r="O244" s="3"/>
@@ -28481,11 +28475,11 @@
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
       <c t="s" r="E245" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="F245" s="2"/>
       <c t="s" r="G245" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="H245" s="3"/>
       <c r="I245" s="9"/>
@@ -28494,7 +28488,7 @@
       </c>
       <c r="K245" s="3"/>
       <c t="s" r="L245" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c t="s" r="M245" s="2">
         <v>41</v>
@@ -28533,14 +28527,14 @@
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
       <c t="s" r="E246" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="F246" s="2"/>
       <c t="s" r="G246" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c t="s" r="H246" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="I246" s="9"/>
       <c t="s" r="J246" s="2">
@@ -28548,10 +28542,10 @@
       </c>
       <c r="K246" s="3"/>
       <c t="s" r="L246" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c t="s" r="M246" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="N246" s="5"/>
       <c r="O246" s="3"/>
@@ -28587,25 +28581,25 @@
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
       <c t="s" r="E247" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="F247" s="2"/>
       <c t="s" r="G247" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c t="s" r="H247" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="I247" s="9"/>
       <c t="s" r="J247" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K247" s="3"/>
       <c t="s" r="L247" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c t="s" r="M247" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="N247" s="5"/>
       <c r="O247" s="3"/>
@@ -28641,11 +28635,11 @@
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
       <c t="s" r="E248" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="F248" s="2"/>
       <c t="s" r="G248" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="H248" s="3"/>
       <c r="I248" s="9"/>
@@ -28654,10 +28648,10 @@
       </c>
       <c r="K248" s="3"/>
       <c t="s" r="L248" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c t="s" r="M248" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N248" s="5"/>
       <c r="O248" s="3"/>
@@ -28693,11 +28687,11 @@
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
       <c t="s" r="E249" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F249" s="2"/>
       <c t="s" r="G249" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="H249" s="3"/>
       <c r="I249" s="9"/>
@@ -28706,10 +28700,10 @@
       </c>
       <c r="K249" s="3"/>
       <c t="s" r="L249" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c t="s" r="M249" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N249" s="5"/>
       <c r="O249" s="3"/>
@@ -28745,23 +28739,23 @@
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
       <c t="s" r="E250" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F250" s="2"/>
       <c t="s" r="G250" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="H250" s="3"/>
       <c r="I250" s="9"/>
       <c t="s" r="J250" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="K250" s="3"/>
       <c t="s" r="L250" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c t="s" r="M250" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="N250" s="5"/>
       <c r="O250" s="3"/>
@@ -28797,23 +28791,23 @@
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
       <c t="s" r="E251" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="F251" s="2"/>
       <c t="s" r="G251" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="H251" s="3"/>
       <c r="I251" s="9"/>
       <c t="s" r="J251" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K251" s="3"/>
       <c t="s" r="L251" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c t="s" r="M251" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="N251" s="5"/>
       <c r="O251" s="3"/>
@@ -28849,11 +28843,11 @@
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
       <c t="s" r="E252" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F252" s="2"/>
       <c t="s" r="G252" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="H252" s="3"/>
       <c r="I252" s="9"/>
@@ -28862,10 +28856,10 @@
       </c>
       <c r="K252" s="3"/>
       <c t="s" r="L252" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c t="s" r="M252" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N252" s="5"/>
       <c r="O252" s="3"/>
@@ -28901,11 +28895,11 @@
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
       <c t="s" r="E253" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F253" s="2"/>
       <c t="s" r="G253" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="H253" s="3"/>
       <c r="I253" s="9"/>
@@ -28914,10 +28908,10 @@
       </c>
       <c r="K253" s="3"/>
       <c t="s" r="L253" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c t="s" r="M253" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="N253" s="5"/>
       <c r="O253" s="3"/>
@@ -28953,11 +28947,11 @@
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
       <c t="s" r="E254" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="F254" s="2"/>
       <c t="s" r="G254" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="H254" s="3"/>
       <c r="I254" s="9"/>
@@ -28966,10 +28960,10 @@
       </c>
       <c r="K254" s="3"/>
       <c t="s" r="L254" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c t="s" r="M254" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="N254" s="5"/>
       <c r="O254" s="3"/>
@@ -29005,11 +28999,11 @@
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
       <c t="s" r="E255" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="F255" s="2"/>
       <c t="s" r="G255" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="H255" s="3"/>
       <c r="I255" s="9"/>
@@ -29018,7 +29012,7 @@
       </c>
       <c r="K255" s="3"/>
       <c t="s" r="L255" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c t="s" r="M255" s="2">
         <v>305</v>
@@ -29057,11 +29051,11 @@
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
       <c t="s" r="E256" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="F256" s="2"/>
       <c t="s" r="G256" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="H256" s="3"/>
       <c r="I256" s="9"/>
@@ -29070,10 +29064,10 @@
       </c>
       <c r="K256" s="3"/>
       <c t="s" r="L256" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c t="s" r="M256" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N256" s="5"/>
       <c r="O256" s="3"/>
@@ -29103,7 +29097,7 @@
       <c r="Y256" s="2"/>
       <c r="Z256" s="2"/>
       <c t="s" r="AA256" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="257" ht="15" customHeight="1">
@@ -29111,22 +29105,22 @@
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
       <c t="s" r="E257" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="F257" s="2"/>
       <c t="s" r="G257" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c t="s" r="H257" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="I257" s="9"/>
       <c t="s" r="J257" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="K257" s="3"/>
       <c t="s" r="L257" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c t="s" r="M257" s="2">
         <v>167</v>
@@ -29165,14 +29159,14 @@
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
       <c t="s" r="E258" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="F258" s="2"/>
       <c t="s" r="G258" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c t="s" r="H258" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="I258" s="9"/>
       <c t="s" r="J258" s="2">
@@ -29180,7 +29174,7 @@
       </c>
       <c r="K258" s="3"/>
       <c t="s" r="L258" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c t="s" r="M258" s="2">
         <v>167</v>
@@ -29219,23 +29213,23 @@
       <c r="B259" s="8"/>
       <c r="C259" s="8"/>
       <c t="s" r="E259" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="F259" s="2"/>
       <c t="s" r="G259" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="H259" s="3"/>
       <c r="I259" s="9"/>
       <c t="s" r="J259" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K259" s="3"/>
       <c t="s" r="L259" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c t="s" r="M259" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N259" s="5"/>
       <c r="O259" s="3"/>
@@ -29265,7 +29259,7 @@
       <c r="Y259" s="2"/>
       <c r="Z259" s="2"/>
       <c t="s" r="AA259" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -29273,11 +29267,11 @@
       <c r="B260" s="8"/>
       <c r="C260" s="8"/>
       <c t="s" r="E260" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="F260" s="2"/>
       <c t="s" r="G260" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H260" s="3"/>
       <c r="I260" s="9"/>
@@ -29286,7 +29280,7 @@
       </c>
       <c r="K260" s="3"/>
       <c t="s" r="L260" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c t="s" r="M260" s="2">
         <v>85</v>
@@ -29319,7 +29313,7 @@
       <c r="Y260" s="2"/>
       <c r="Z260" s="2"/>
       <c t="s" r="AA260" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="261" ht="15" customHeight="1">
@@ -29327,11 +29321,11 @@
       <c r="B261" s="8"/>
       <c r="C261" s="8"/>
       <c t="s" r="E261" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="F261" s="2"/>
       <c t="s" r="G261" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="H261" s="3"/>
       <c r="I261" s="9"/>
@@ -29340,10 +29334,10 @@
       </c>
       <c r="K261" s="3"/>
       <c t="s" r="L261" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c t="s" r="M261" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="N261" s="5"/>
       <c r="O261" s="3"/>
@@ -29379,20 +29373,20 @@
       <c r="B262" s="8"/>
       <c r="C262" s="8"/>
       <c t="s" r="E262" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="F262" s="2"/>
       <c t="s" r="G262" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="H262" s="3"/>
       <c r="I262" s="9"/>
       <c t="s" r="J262" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K262" s="3"/>
       <c t="s" r="L262" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c t="s" r="M262" s="2">
         <v>41</v>
@@ -29425,7 +29419,7 @@
       <c r="Y262" s="2"/>
       <c r="Z262" s="2"/>
       <c t="s" r="AA262" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="263" ht="15" customHeight="1">
@@ -29433,14 +29427,14 @@
       <c r="B263" s="8"/>
       <c r="C263" s="8"/>
       <c t="s" r="E263" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F263" s="2"/>
       <c t="s" r="G263" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c t="s" r="H263" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="I263" s="9"/>
       <c t="s" r="J263" s="2">
@@ -29448,7 +29442,7 @@
       </c>
       <c r="K263" s="3"/>
       <c t="s" r="L263" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c t="s" r="M263" s="2">
         <v>141</v>
@@ -29487,25 +29481,25 @@
       <c r="B264" s="8"/>
       <c r="C264" s="8"/>
       <c t="s" r="E264" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="F264" s="2"/>
       <c t="s" r="G264" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c t="s" r="H264" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="I264" s="9"/>
       <c t="s" r="J264" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="K264" s="3"/>
       <c t="s" r="L264" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c t="s" r="M264" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="N264" s="5"/>
       <c r="O264" s="3"/>
@@ -29541,11 +29535,11 @@
       <c r="B265" s="8"/>
       <c r="C265" s="8"/>
       <c t="s" r="E265" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="F265" s="2"/>
       <c t="s" r="G265" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="H265" s="3"/>
       <c r="I265" s="9"/>
@@ -29554,10 +29548,10 @@
       </c>
       <c r="K265" s="3"/>
       <c t="s" r="L265" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c t="s" r="M265" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="N265" s="5"/>
       <c r="O265" s="3"/>
@@ -29593,11 +29587,11 @@
       <c r="B266" s="8"/>
       <c r="C266" s="8"/>
       <c t="s" r="E266" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="F266" s="2"/>
       <c t="s" r="G266" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="H266" s="3"/>
       <c r="I266" s="9"/>
@@ -29606,10 +29600,10 @@
       </c>
       <c r="K266" s="3"/>
       <c t="s" r="L266" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c t="s" r="M266" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="N266" s="5"/>
       <c r="O266" s="3"/>
@@ -29645,14 +29639,14 @@
       <c r="B267" s="8"/>
       <c r="C267" s="8"/>
       <c t="s" r="E267" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="F267" s="2"/>
       <c t="s" r="G267" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c t="s" r="H267" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="I267" s="9"/>
       <c t="s" r="J267" s="2">
@@ -29660,10 +29654,10 @@
       </c>
       <c r="K267" s="3"/>
       <c t="s" r="L267" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c t="s" r="M267" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="N267" s="5"/>
       <c r="O267" s="3"/>
@@ -29699,22 +29693,22 @@
       <c r="B268" s="8"/>
       <c r="C268" s="8"/>
       <c t="s" r="E268" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F268" s="2"/>
       <c t="s" r="G268" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c t="s" r="H268" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="I268" s="9"/>
       <c t="s" r="J268" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K268" s="3"/>
       <c t="s" r="L268" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c t="s" r="M268" s="2">
         <v>275</v>
@@ -29753,11 +29747,11 @@
       <c r="B269" s="8"/>
       <c r="C269" s="8"/>
       <c t="s" r="E269" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="F269" s="2"/>
       <c t="s" r="G269" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="H269" s="3"/>
       <c r="I269" s="9"/>
@@ -29766,10 +29760,10 @@
       </c>
       <c r="K269" s="3"/>
       <c t="s" r="L269" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c t="s" r="M269" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="N269" s="5"/>
       <c r="O269" s="3"/>
@@ -29805,11 +29799,11 @@
       <c r="B270" s="8"/>
       <c r="C270" s="8"/>
       <c t="s" r="E270" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="F270" s="2"/>
       <c t="s" r="G270" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="H270" s="3"/>
       <c r="I270" s="9"/>
@@ -29818,10 +29812,10 @@
       </c>
       <c r="K270" s="3"/>
       <c t="s" r="L270" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c t="s" r="M270" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="N270" s="5"/>
       <c r="O270" s="3"/>
@@ -29857,23 +29851,23 @@
       <c r="B271" s="8"/>
       <c r="C271" s="8"/>
       <c t="s" r="E271" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="F271" s="2"/>
       <c t="s" r="G271" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="H271" s="3"/>
       <c r="I271" s="9"/>
       <c t="s" r="J271" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K271" s="3"/>
       <c t="s" r="L271" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c t="s" r="M271" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N271" s="5"/>
       <c r="O271" s="3"/>
@@ -29909,11 +29903,11 @@
       <c r="B272" s="8"/>
       <c r="C272" s="8"/>
       <c t="s" r="E272" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="F272" s="2"/>
       <c t="s" r="G272" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="H272" s="3"/>
       <c r="I272" s="9"/>
@@ -29922,10 +29916,10 @@
       </c>
       <c r="K272" s="3"/>
       <c t="s" r="L272" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c t="s" r="M272" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N272" s="5"/>
       <c r="O272" s="3"/>
@@ -29961,23 +29955,23 @@
       <c r="B273" s="8"/>
       <c r="C273" s="8"/>
       <c t="s" r="E273" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="F273" s="2"/>
       <c t="s" r="G273" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="H273" s="3"/>
       <c r="I273" s="9"/>
       <c t="s" r="J273" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="K273" s="3"/>
       <c t="s" r="L273" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c t="s" r="M273" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="N273" s="5"/>
       <c r="O273" s="3"/>
@@ -30013,23 +30007,23 @@
       <c r="B274" s="8"/>
       <c r="C274" s="8"/>
       <c t="s" r="E274" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="F274" s="2"/>
       <c t="s" r="G274" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="H274" s="3"/>
       <c r="I274" s="9"/>
       <c t="s" r="J274" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K274" s="3"/>
       <c t="s" r="L274" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c t="s" r="M274" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N274" s="5"/>
       <c r="O274" s="3"/>
@@ -30065,23 +30059,23 @@
       <c r="B275" s="8"/>
       <c r="C275" s="8"/>
       <c t="s" r="E275" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="F275" s="2"/>
       <c t="s" r="G275" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="H275" s="3"/>
       <c r="I275" s="9"/>
       <c t="s" r="J275" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="K275" s="3"/>
       <c t="s" r="L275" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c t="s" r="M275" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="N275" s="5"/>
       <c r="O275" s="3"/>
@@ -30117,11 +30111,11 @@
       <c r="B276" s="8"/>
       <c r="C276" s="8"/>
       <c t="s" r="E276" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="F276" s="2"/>
       <c t="s" r="G276" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="H276" s="3"/>
       <c r="I276" s="9"/>
@@ -30130,7 +30124,7 @@
       </c>
       <c r="K276" s="3"/>
       <c t="s" r="L276" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c t="s" r="M276" s="2">
         <v>85</v>
@@ -30163,7 +30157,7 @@
       <c r="Y276" s="2"/>
       <c r="Z276" s="2"/>
       <c t="s" r="AA276" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="277" ht="15" customHeight="1">
@@ -30171,23 +30165,23 @@
       <c r="B277" s="8"/>
       <c r="C277" s="8"/>
       <c t="s" r="E277" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="F277" s="2"/>
       <c t="s" r="G277" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="H277" s="3"/>
       <c r="I277" s="9"/>
       <c t="s" r="J277" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K277" s="3"/>
       <c t="s" r="L277" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c t="s" r="M277" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="N277" s="5"/>
       <c r="O277" s="3"/>
@@ -30223,14 +30217,14 @@
       <c r="B278" s="8"/>
       <c r="C278" s="8"/>
       <c t="s" r="E278" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="F278" s="2"/>
       <c t="s" r="G278" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c t="s" r="H278" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="I278" s="9"/>
       <c t="s" r="J278" s="2">
@@ -30238,10 +30232,10 @@
       </c>
       <c r="K278" s="3"/>
       <c t="s" r="L278" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c t="s" r="M278" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="N278" s="5"/>
       <c r="O278" s="3"/>
@@ -30277,25 +30271,25 @@
       <c r="B279" s="8"/>
       <c r="C279" s="8"/>
       <c t="s" r="E279" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="F279" s="2"/>
       <c t="s" r="G279" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c t="s" r="H279" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="I279" s="9"/>
       <c t="s" r="J279" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="K279" s="3"/>
       <c t="s" r="L279" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c t="s" r="M279" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="N279" s="5"/>
       <c r="O279" s="3"/>
@@ -30331,25 +30325,25 @@
       <c r="B280" s="8"/>
       <c r="C280" s="8"/>
       <c t="s" r="E280" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="F280" s="2"/>
       <c t="s" r="G280" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c t="s" r="H280" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="I280" s="9"/>
       <c t="s" r="J280" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K280" s="3"/>
       <c t="s" r="L280" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c t="s" r="M280" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N280" s="5"/>
       <c r="O280" s="3"/>
@@ -30385,11 +30379,11 @@
       <c r="B281" s="8"/>
       <c r="C281" s="8"/>
       <c t="s" r="E281" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="F281" s="2"/>
       <c t="s" r="G281" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="H281" s="3"/>
       <c r="I281" s="9"/>
@@ -30398,10 +30392,10 @@
       </c>
       <c r="K281" s="3"/>
       <c t="s" r="L281" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c t="s" r="M281" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="N281" s="5"/>
       <c r="O281" s="3"/>
@@ -30437,20 +30431,20 @@
       <c r="B282" s="8"/>
       <c r="C282" s="8"/>
       <c t="s" r="E282" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="F282" s="2"/>
       <c t="s" r="G282" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="H282" s="3"/>
       <c r="I282" s="9"/>
       <c t="s" r="J282" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K282" s="3"/>
       <c t="s" r="L282" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c t="s" r="M282" s="2">
         <v>85</v>
@@ -30483,7 +30477,7 @@
       <c r="Y282" s="2"/>
       <c r="Z282" s="2"/>
       <c t="s" r="AA282" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="283" ht="15" customHeight="1">
@@ -30491,23 +30485,23 @@
       <c r="B283" s="8"/>
       <c r="C283" s="8"/>
       <c t="s" r="E283" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="F283" s="2"/>
       <c t="s" r="G283" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="H283" s="3"/>
       <c r="I283" s="9"/>
       <c t="s" r="J283" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="K283" s="3"/>
       <c t="s" r="L283" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c t="s" r="M283" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="N283" s="5"/>
       <c r="O283" s="3"/>
@@ -30543,11 +30537,11 @@
       <c r="B284" s="8"/>
       <c r="C284" s="8"/>
       <c t="s" r="E284" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="F284" s="2"/>
       <c t="s" r="G284" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="H284" s="3"/>
       <c r="I284" s="9"/>
@@ -30556,10 +30550,10 @@
       </c>
       <c r="K284" s="3"/>
       <c t="s" r="L284" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c t="s" r="M284" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="N284" s="5"/>
       <c r="O284" s="3"/>
@@ -30595,11 +30589,11 @@
       <c r="B285" s="8"/>
       <c r="C285" s="8"/>
       <c t="s" r="E285" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="F285" s="2"/>
       <c t="s" r="G285" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="H285" s="3"/>
       <c r="I285" s="9"/>
@@ -30608,10 +30602,10 @@
       </c>
       <c r="K285" s="3"/>
       <c t="s" r="L285" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c t="s" r="M285" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="N285" s="5"/>
       <c r="O285" s="3"/>
@@ -30647,11 +30641,11 @@
       <c r="B286" s="8"/>
       <c r="C286" s="8"/>
       <c t="s" r="E286" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="F286" s="2"/>
       <c t="s" r="G286" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="H286" s="3"/>
       <c r="I286" s="9"/>
@@ -30660,7 +30654,7 @@
       </c>
       <c r="K286" s="3"/>
       <c t="s" r="L286" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c t="s" r="M286" s="2">
         <v>225</v>
@@ -30699,23 +30693,23 @@
       <c r="B287" s="8"/>
       <c r="C287" s="8"/>
       <c t="s" r="E287" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="F287" s="2"/>
       <c t="s" r="G287" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="H287" s="3"/>
       <c r="I287" s="9"/>
       <c t="s" r="J287" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="K287" s="3"/>
       <c t="s" r="L287" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c t="s" r="M287" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N287" s="5"/>
       <c r="O287" s="3"/>
@@ -30749,7 +30743,7 @@
     <row r="288" ht="12.75" customHeight="1">
       <c r="A288" s="8"/>
       <c t="s" r="C288" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="D288" s="2"/>
       <c r="E288" s="2"/>
@@ -30786,7 +30780,7 @@
       <c r="A289" s="8"/>
       <c r="B289" s="8"/>
       <c t="s" r="D289" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="E289" s="2"/>
       <c r="F289" s="2"/>
@@ -30798,10 +30792,10 @@
       </c>
       <c r="K289" s="3"/>
       <c t="s" r="L289" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c t="s" r="M289" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="N289" s="5"/>
       <c r="O289" s="3"/>
@@ -30817,7 +30811,7 @@
         <v>0</v>
       </c>
       <c t="s" r="U289" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c t="s" r="V289" s="2">
         <v>33</v>
@@ -30826,7 +30820,7 @@
         <v>34</v>
       </c>
       <c t="s" r="X289" s="2">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="Y289" s="2"/>
       <c r="Z289" s="2"/>
@@ -30836,7 +30830,7 @@
       <c r="A290" s="8"/>
       <c r="B290" s="8"/>
       <c t="s" r="D290" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="E290" s="2"/>
       <c r="F290" s="2"/>
@@ -30848,10 +30842,10 @@
       </c>
       <c r="K290" s="3"/>
       <c t="s" r="L290" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c t="s" r="M290" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="N290" s="5"/>
       <c r="O290" s="3"/>
@@ -30867,7 +30861,7 @@
         <v>0</v>
       </c>
       <c t="s" r="U290" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c t="s" r="V290" s="2">
         <v>33</v>
@@ -30876,7 +30870,7 @@
         <v>34</v>
       </c>
       <c t="s" r="X290" s="2">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="Y290" s="2"/>
       <c r="Z290" s="2"/>
@@ -30886,7 +30880,7 @@
       <c r="A291" s="8"/>
       <c r="B291" s="8"/>
       <c t="s" r="D291" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="E291" s="2"/>
       <c r="F291" s="2"/>
@@ -30894,14 +30888,14 @@
       <c r="H291" s="3"/>
       <c r="I291" s="9"/>
       <c t="s" r="J291" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="K291" s="3"/>
       <c t="s" r="L291" s="2">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c t="s" r="M291" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="N291" s="5"/>
       <c r="O291" s="3"/>
@@ -30917,7 +30911,7 @@
         <v>0</v>
       </c>
       <c t="s" r="U291" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c t="s" r="V291" s="2">
         <v>33</v>
@@ -30936,7 +30930,7 @@
       <c r="A292" s="8"/>
       <c r="B292" s="8"/>
       <c t="s" r="D292" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="E292" s="2"/>
       <c r="F292" s="2"/>
@@ -30944,14 +30938,14 @@
       <c r="H292" s="3"/>
       <c r="I292" s="9"/>
       <c t="s" r="J292" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="K292" s="3"/>
       <c t="s" r="L292" s="2">
+        <v>926</v>
+      </c>
+      <c t="s" r="M292" s="2">
         <v>924</v>
-      </c>
-      <c t="s" r="M292" s="2">
-        <v>922</v>
       </c>
       <c r="N292" s="5"/>
       <c r="O292" s="3"/>
@@ -30967,7 +30961,7 @@
         <v>0</v>
       </c>
       <c t="s" r="U292" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c t="s" r="V292" s="2">
         <v>33</v>
@@ -30985,7 +30979,7 @@
     <row r="293" ht="12.75" customHeight="1">
       <c r="A293" s="8"/>
       <c t="s" r="C293" s="2">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="D293" s="2"/>
       <c r="E293" s="2"/>
@@ -31022,7 +31016,7 @@
       <c r="A294" s="8"/>
       <c r="B294" s="8"/>
       <c t="s" r="D294" s="2">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="E294" s="2"/>
       <c r="F294" s="2"/>
@@ -31030,14 +31024,14 @@
       <c r="H294" s="3"/>
       <c r="I294" s="9"/>
       <c t="s" r="J294" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="K294" s="3"/>
       <c t="s" r="L294" s="2">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c t="s" r="M294" s="2">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="N294" s="5"/>
       <c r="O294" s="3"/>
@@ -31062,7 +31056,7 @@
         <v>34</v>
       </c>
       <c t="s" r="X294" s="2">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="Y294" s="2"/>
       <c r="Z294" s="2"/>
@@ -31206,12 +31200,12 @@
     <mergeCell ref="A91:D91"/>
     <mergeCell ref="A92:D92"/>
     <mergeCell ref="A93:D93"/>
-    <mergeCell ref="A94:C94"/>
-    <mergeCell ref="E94:F94"/>
-    <mergeCell ref="A95:D95"/>
-    <mergeCell ref="A96:C96"/>
-    <mergeCell ref="E96:F96"/>
-    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A97:C97"/>
+    <mergeCell ref="E97:F97"/>
     <mergeCell ref="A98:D98"/>
     <mergeCell ref="A99:D99"/>
     <mergeCell ref="A100:D100"/>

--- a/data/airports/Export APT 4.xlsx
+++ b/data/airports/Export APT 4.xlsx
@@ -944,25 +944,25 @@
     <t>CROATIE (0 / 4)</t>
   </si>
   <si>
+    <t>davorpuljevic-airport-lddu-dubrovnik</t>
+  </si>
+  <si>
+    <t>LDDU</t>
+  </si>
+  <si>
+    <t>Puljevic</t>
+  </si>
+  <si>
+    <t>inibuilds-airport-lddu-dubrovnik</t>
+  </si>
+  <si>
+    <t>LDDU Dubrovnik</t>
+  </si>
+  <si>
     <t>davorpuljevic-airport-ldsp-split</t>
   </si>
   <si>
     <t>LDSP</t>
-  </si>
-  <si>
-    <t>Puljevic</t>
-  </si>
-  <si>
-    <t>davorpuljevic-airport-lddu-dubrovnik</t>
-  </si>
-  <si>
-    <t>LDDU</t>
-  </si>
-  <si>
-    <t>inibuilds-airport-lddu-dubrovnik</t>
-  </si>
-  <si>
-    <t>LDDU Dubrovnik</t>
   </si>
   <si>
     <t>aerosoft-airport-ldza-zagreb</t>
@@ -20810,11 +20810,15 @@
       <c t="s" r="F91" s="2">
         <v>311</v>
       </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="3"/>
+      <c t="s" r="G91" s="2">
+        <v>312</v>
+      </c>
+      <c t="s" r="H91" s="2">
+        <v>312</v>
+      </c>
       <c r="I91" s="9"/>
       <c t="s" r="J91" s="2">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="K91" s="3"/>
       <c t="s" r="L91" s="2">
@@ -20861,21 +20865,21 @@
         <v>314</v>
       </c>
       <c t="s" r="G92" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c t="s" r="H92" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I92" s="9"/>
       <c t="s" r="J92" s="2">
-        <v>176</v>
+        <v>55</v>
       </c>
       <c r="K92" s="3"/>
       <c t="s" r="L92" s="2">
         <v>315</v>
       </c>
       <c t="s" r="M92" s="2">
-        <v>313</v>
+        <v>41</v>
       </c>
       <c r="N92" s="5"/>
       <c r="O92" s="3"/>
@@ -20915,21 +20919,19 @@
         <v>316</v>
       </c>
       <c t="s" r="G93" s="2">
-        <v>315</v>
-      </c>
-      <c t="s" r="H93" s="2">
-        <v>315</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="H93" s="3"/>
       <c r="I93" s="9"/>
       <c t="s" r="J93" s="2">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="K93" s="3"/>
       <c t="s" r="L93" s="2">
         <v>317</v>
       </c>
       <c t="s" r="M93" s="2">
-        <v>41</v>
+        <v>313</v>
       </c>
       <c r="N93" s="5"/>
       <c r="O93" s="3"/>
